--- a/docs/xlsx/jobs-2026-10-15.xlsx
+++ b/docs/xlsx/jobs-2026-10-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="631">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,45 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Admissions Officer</t>
+  </si>
+  <si>
+    <t>Archipelagos Institute of Marine Conservation</t>
+  </si>
+  <si>
+    <t>Agios Konstantinos, Samos, Europe</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Salary commensurate with experience.</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-admissions-officer-agios-konstantinos-samos-europe/7880584135</t>
+  </si>
+  <si>
+    <t>Animal Collections Manager</t>
+  </si>
+  <si>
+    <t>White Oak Conservation</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Negotiable</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-collections-manager-yulee-florida/8603220102</t>
+  </si>
+  <si>
     <t>Assistant Professor - Precision Ranching</t>
   </si>
   <si>
@@ -61,6 +100,21 @@
     <t>https://www.conservationjobboard.com/job-listing-assistant-professor---precision-ranching-sonora-and-san-angelo-texas/3095351797</t>
   </si>
   <si>
+    <t>Campaign Manager</t>
+  </si>
+  <si>
+    <t>Grow the Flow</t>
+  </si>
+  <si>
+    <t>Salt Lake City, UT</t>
+  </si>
+  <si>
+    <t>$60,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campaign-manager-salt-lake-city-utah/3152890062</t>
+  </si>
+  <si>
     <t>Community Assistance Fellow – AmeriCorps</t>
   </si>
   <si>
@@ -82,24 +136,93 @@
     <t>https://www.conservationjobboard.com/job-listing-community-assistance-fellow--americorps-westlake-village-california/4884246627</t>
   </si>
   <si>
+    <t>Conservation and Disaster Response Crew Members and Leaders | Austin, TX</t>
+  </si>
+  <si>
+    <t>Texas Conservation Corps of American YouthWorks</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$2,400 - $2,720 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-and-disaster-response-crew-members-and-leaders-austin-texas/7118759639</t>
+  </si>
+  <si>
+    <t>Conservation and Disaster Response Crew Members and Leaders | Houston, TX</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-and-disaster-response-crew-members-and-leaders--houston-tx-houston-texas/3050934100</t>
+  </si>
+  <si>
+    <t>Conservation and Disaster Response Team Members and Leaders | Oklahoma City, OK</t>
+  </si>
+  <si>
+    <t>Oklahoma Conservation Corps of American YouthWorks</t>
+  </si>
+  <si>
+    <t>Oklahoma City, OK</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-and-disaster-response-team-members-and-leaders--oklahoma-city-ok-oklahoma-city-oklahoma/9097780483</t>
+  </si>
+  <si>
+    <t>Conservation Technician III - Division of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Felton, DE</t>
+  </si>
+  <si>
+    <t>$39,674.86 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-technician-iii---division-of-fish-and-wildlife-felton-delaware/3003283412</t>
+  </si>
+  <si>
+    <t>Conservation Technician Supervisor - Division of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>$47,804.40 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-technician-supervisor---division-of-fish-and-wildlife-felton-delaware/1770251844</t>
+  </si>
+  <si>
+    <t>Digital &amp; Social Media Specialist</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-digital--social-media-specialist-salt-lake-city-utah/9927319210</t>
+  </si>
+  <si>
     <t>Eagle Studies Field Technician</t>
   </si>
   <si>
     <t>HawkWatch International</t>
   </si>
   <si>
-    <t>Salt Lake City, UT</t>
-  </si>
-  <si>
     <t>Temporary</t>
   </si>
   <si>
     <t>$3,100 per month</t>
   </si>
   <si>
-    <t>wildlife</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-eagle-studies-field-technician-salt-lake-city-utah/7390918559</t>
   </si>
   <si>
@@ -112,9 +235,6 @@
     <t>Cedar Mountain, NC</t>
   </si>
   <si>
-    <t>Permanent</t>
-  </si>
-  <si>
     <t>$40,000 - $45,000 per year</t>
   </si>
   <si>
@@ -148,6 +268,21 @@
     <t>https://www.conservationjobboard.com/job-listing-environmental-science-educator-el-portal-california/4426815061</t>
   </si>
   <si>
+    <t>Environmental Scientist (41579)</t>
+  </si>
+  <si>
+    <t>Hanford Mission Integration Solutions</t>
+  </si>
+  <si>
+    <t>Richland, WA</t>
+  </si>
+  <si>
+    <t>$90,150 - $166,263 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-41579-richland-washington/1322093203</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -166,6 +301,75 @@
     <t>https://www.conservationjobboard.com/job-listing-executive-director-cave-junction-oregon/9096854027</t>
   </si>
   <si>
+    <t>Field Coordinator</t>
+  </si>
+  <si>
+    <t>Montana Conservation Corps</t>
+  </si>
+  <si>
+    <t>Bozeman, MT</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-coordinator-bozeman-montana/4835191345</t>
+  </si>
+  <si>
+    <t>Field Crew Leader (Backcountry, Forestry, Fuels, Trails)</t>
+  </si>
+  <si>
+    <t>Bozeman, Helena, Kalispell, Missoula, MT</t>
+  </si>
+  <si>
+    <t>$2,720 per month</t>
+  </si>
+  <si>
+    <t>forestry-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-crew-leader-bozeman-helena-kalispell-missoula-montana/8436844424</t>
+  </si>
+  <si>
+    <t>Fisheries Technician</t>
+  </si>
+  <si>
+    <t>Confederated Tribes of Warm Springs</t>
+  </si>
+  <si>
+    <t>Hood River, OR</t>
+  </si>
+  <si>
+    <t>$19 - $25 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-hood-river-oregon/1054796890</t>
+  </si>
+  <si>
+    <t>Graduate Assistantship (PhD/MS) in Spatial Hydrology or Riverscape Assessment</t>
+  </si>
+  <si>
+    <t>Texas State University</t>
+  </si>
+  <si>
+    <t>San Marcos, TX</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$15,676.47 - $31,615.65 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-graduate-assistantship-phdms-in-spatial-hydrology-or-riverscape-assessment-san-marcos-texas/6624640381</t>
+  </si>
+  <si>
     <t>Grants &amp; Finance Specialist</t>
   </si>
   <si>
@@ -178,12 +382,27 @@
     <t>$40.15 - $45.19 per hour</t>
   </si>
   <si>
-    <t>admin-leadership</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-grants--finance-specialist-soquel-california/3173852846</t>
   </si>
   <si>
+    <t>Habitat Management Biologist</t>
+  </si>
+  <si>
+    <t>NH Fish &amp; Game Department</t>
+  </si>
+  <si>
+    <t>Concord, NH</t>
+  </si>
+  <si>
+    <t>$25.40 - $34.14 per hour</t>
+  </si>
+  <si>
+    <t>forestry-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-management-biologist-concord-new-hampshire/5373577188</t>
+  </si>
+  <si>
     <t>Heavy Equipment Operator (HEO)</t>
   </si>
   <si>
@@ -202,6 +421,45 @@
     <t>https://www.conservationjobboard.com/job-listing-heavy-equipment-operator-heo-flemington-georgia/3769773164</t>
   </si>
   <si>
+    <t>Land Stewardship Intern</t>
+  </si>
+  <si>
+    <t>Iowa Natural Heritage Foundation</t>
+  </si>
+  <si>
+    <t>Des Moines, IA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$15 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-stewardship-intern-des-moines-iowa/6165841795</t>
+  </si>
+  <si>
+    <t>Marine Science Instructor -- Shared Housing, Meals, and Ocean Fun included</t>
+  </si>
+  <si>
+    <t>Seacamp</t>
+  </si>
+  <si>
+    <t>Big Pine Key, FL</t>
+  </si>
+  <si>
+    <t>$1,100 - $1,300 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-science-instructor----shared-housing-meals-and-ocean-fun-included-big-pine-key-florida/1459463722</t>
+  </si>
+  <si>
     <t>Otolith Laboratory Biologist - Fish &amp; Wildlife Biologist 3 - Permanent - 2026-08568</t>
   </si>
   <si>
@@ -220,6 +478,36 @@
     <t>https://www.conservationjobboard.com/job-listing-otolith-laboratory-biologist---fish--wildlife-biologist-3---permanent---2026-08568-olympia-washington/5952151835</t>
   </si>
   <si>
+    <t>Outdoor Education/Field Study Instructor/Naturalist</t>
+  </si>
+  <si>
+    <t>Clemson University Learning Institute</t>
+  </si>
+  <si>
+    <t>Pickens, SC</t>
+  </si>
+  <si>
+    <t>$525 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-educationfield-study-instructornaturalist-pickens-south-carolina/6306669806</t>
+  </si>
+  <si>
+    <t>Prairie Grouse Aviculture Internship</t>
+  </si>
+  <si>
+    <t>George Miksch Sutton Avian Research Center</t>
+  </si>
+  <si>
+    <t>Bartlesville, OK</t>
+  </si>
+  <si>
+    <t>$7.25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-prairie-grouse-aviculture-internship-bartlesville-oklahoma/4820197228</t>
+  </si>
+  <si>
     <t>Program Associate</t>
   </si>
   <si>
@@ -238,6 +526,114 @@
     <t>https://www.conservationjobboard.com/job-listing-we-plant-it-forward-program-associate-raleighdurham-area-north-carolina/8352411068</t>
   </si>
   <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>Clear Lake Environmental Research Center</t>
+  </si>
+  <si>
+    <t>Lakeport, CA</t>
+  </si>
+  <si>
+    <t>$30 - $40 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-coordinator-lakeport-california/1955820997</t>
+  </si>
+  <si>
+    <t>Public Affairs Intern</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, CA</t>
+  </si>
+  <si>
+    <t>$27.94 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-affairs-intern-los-altos-ca-california/1497131136</t>
+  </si>
+  <si>
+    <t>Real Estate Manager, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>The Conservation Fund</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>$55,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-real-estate-manager-mid-atlantic-arlington-virginia/7285843926</t>
+  </si>
+  <si>
+    <t>Recruitment Assistant</t>
+  </si>
+  <si>
+    <t>Bozeman, Helena, Kalispell, or Missoula (remote/hybrid), MT</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-recruitment-assistant-bozeman-helena-kalispell-or-missoula-remotehybrid-montana/7275573197</t>
+  </si>
+  <si>
+    <t>Sanctuary Land Technician</t>
+  </si>
+  <si>
+    <t>Southern Wisconsin Bird Alliance</t>
+  </si>
+  <si>
+    <t>Arlington, WI</t>
+  </si>
+  <si>
+    <t>$32-$36k per year depending on qualifications, PLUS residential benefit of living rent and utility free on site (valued at $28k/year)</t>
+  </si>
+  <si>
+    <t>botany-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sanctuary-land-technician-arlington-wisconsin/6377172369</t>
+  </si>
+  <si>
+    <t>Santa Cruz Island Restoration Technician</t>
+  </si>
+  <si>
+    <t>California Institute of Environmental Studies</t>
+  </si>
+  <si>
+    <t>Ventura, CA</t>
+  </si>
+  <si>
+    <t>$22.29 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-santa-cruz-island-restoration-technician-ventura-california/7446792320</t>
+  </si>
+  <si>
+    <t>Santa Rosa Island Seasonal Invasive Plant Technician</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-santa-rosa-island-seasonal-invasive-plant-technician-ventura-california/8617426321</t>
+  </si>
+  <si>
     <t>Sea Turtle Lighting Biologist</t>
   </si>
   <si>
@@ -274,6 +670,69 @@
     <t>https://www.conservationjobboard.com/job-listing-state-heritage-botanist-research-scientist-2-sauk-rapids-minnesota/3534595062</t>
   </si>
   <si>
+    <t>Summer Research Fellow</t>
+  </si>
+  <si>
+    <t>Edmund Niles Huyck Preserve, Inc.</t>
+  </si>
+  <si>
+    <t>Rensselaerville, NY</t>
+  </si>
+  <si>
+    <t>$10,000</t>
+  </si>
+  <si>
+    <t>ecology-land-trust-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-research-fellow-rensselaerville-new-york/3385511501</t>
+  </si>
+  <si>
+    <t>TPWD - Customer Service Representative I</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Comstock, TX</t>
+  </si>
+  <si>
+    <t>$3,245.29 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---customer-service-representative-i-comstock-texas/6078607139</t>
+  </si>
+  <si>
+    <t>USDA-ARS Entomopathogenic Fungi for Biocontrol of Nematodes and Insects</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Ithaca, NY</t>
+  </si>
+  <si>
+    <t>Stipend $3,500.00 – $4,300.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-entomopathogenic-fungi-for-biocontrol-of-nematodes-and-insects-ithaca-new-york/7587222815</t>
+  </si>
+  <si>
+    <t>VP for Finance</t>
+  </si>
+  <si>
+    <t>Society for the Protection of NH Forests</t>
+  </si>
+  <si>
+    <t>$105,000 - $0 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vp-for-finance-concord-new-hampshire/8145834781</t>
+  </si>
+  <si>
     <t>Walking Mountains Graduate Fellowship 2027-2029</t>
   </si>
   <si>
@@ -283,9 +742,6 @@
     <t>Avon, CO</t>
   </si>
   <si>
-    <t>Student</t>
-  </si>
-  <si>
     <t>$17,500 per year</t>
   </si>
   <si>
@@ -308,6 +764,1149 @@
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-water-resources-director-jackson-wyoming/6042756887</t>
+  </si>
+  <si>
+    <t>Wildland Restoration Team Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-restoration-team-leader-bozeman-helena-kalispell-missoula-montana/7632154564</t>
+  </si>
+  <si>
+    <t>Wildlife Habitat Biologist - Montana</t>
+  </si>
+  <si>
+    <t>Bird Conservancy of the Rockies</t>
+  </si>
+  <si>
+    <t>Baker or Ekalaka, MT</t>
+  </si>
+  <si>
+    <t>$58,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-habitat-biologist---montana-baker-or-ekalaka-montana/6543351236</t>
+  </si>
+  <si>
+    <t>Youth Crew Leader</t>
+  </si>
+  <si>
+    <t>Bozeman or Kalispell, MT</t>
+  </si>
+  <si>
+    <t>$2,880 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-youth-crew-leader-bozeman-or-kalispell-montana/3230009045</t>
+  </si>
+  <si>
+    <t>Accounting and Grants Coordinator</t>
+  </si>
+  <si>
+    <t>Research!America</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09c876a132d744378490a03ad7aebabe-accounting-and-grants-coordinator-researchamerica-arlington</t>
+  </si>
+  <si>
+    <t>Administrative and Program Associate</t>
+  </si>
+  <si>
+    <t>League of Women Voters of Massachusetts</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed3960128b614e3980da46d6342f25c1-administrative-and-program-associate-league-of-women-voters-of-massachusetts-boston</t>
+  </si>
+  <si>
+    <t>Afterschool Program Coordinator</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63050df7cab045cea48971770564c5be-afterschool-program-coordinator-harlem-grown-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Archivist</t>
+  </si>
+  <si>
+    <t>The Gilder Lehrman Institute of American History</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df5916926e6c432496f6b79353e9128b-assistant-archivist-the-gilder-lehrman-institute-of-american-history-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General: Taxpayer Protection Bureau(3918)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 91506.00 - 190644.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/5724f197546644ce81473e5cbca9d183-assistant-attorney-general-taxpayer-protection-bureau3918-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Associate Director of Development</t>
+  </si>
+  <si>
+    <t>Shakespeare Theatre Company</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d8763f09f3640dc895af31e0e219b19-associate-director-of-development-shakespeare-theatre-company-washington</t>
+  </si>
+  <si>
+    <t>Associate Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>At The Crossroads</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 89000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f88d69137d1b4a609c7f6df8e6051512-associate-director-of-development-and-communications-at-the-crossroads-san-francisco</t>
+  </si>
+  <si>
+    <t>Associate Director of Events</t>
+  </si>
+  <si>
+    <t>Powered by Professionals</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/67a3c3bb9f0d41c2bc215b4c1eff5353-associate-director-of-events-powered-by-professionals-new-york</t>
+  </si>
+  <si>
+    <t>Associate II, Programs (East)</t>
+  </si>
+  <si>
+    <t>U.S. Soccer Foundation</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04898ef3a5e34464ac6c3ae895f6a50b-associate-ii-programs-east-us-soccer-foundation-washington</t>
+  </si>
+  <si>
+    <t>Attorney Fellow (Economic Justice Initiative at TxILC)</t>
+  </si>
+  <si>
+    <t>Texas Immigration Law Council</t>
+  </si>
+  <si>
+    <t>Edinburg, Texas</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b3049d993ac45faaa4cc164edc90a2e-attorney-fellow-economic-justice-initiative-at-txilc-texas-immigration-law-council-edinburg</t>
+  </si>
+  <si>
+    <t>Building Substitute Teacher</t>
+  </si>
+  <si>
+    <t>Intergenerational Schools</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d501e3999e63407489932db7e9496ef3-building-substitute-teacher-intergenerational-schools-cleveland</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Future Centered Care</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/5bf7b21bf0584829b12db3271c5b1336-case-manager-future-centered-care-new-york</t>
+  </si>
+  <si>
+    <t>Case Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>A Supportive Community For All</t>
+  </si>
+  <si>
+    <t>Carnation, Washington</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 32.82 - 32.82/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be760f3758884e62a975b65409af4b77-case-manager-part-time-a-supportive-community-for-all-carnation</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Ampersand Consulting, New England</t>
+  </si>
+  <si>
+    <t>Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2c76823b1d9b4efd9d38b4a521628d69-chief-development-officer-ampersand-consulting-new-england-hartford</t>
+  </si>
+  <si>
+    <t>Clergy &amp; Religious School Coordinator</t>
+  </si>
+  <si>
+    <t>Congregation Ahavath Chesed- The Temple Jacksonville</t>
+  </si>
+  <si>
+    <t>Jacksonville, Florida</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23eaa08243f4455eabe43dcd410e4096-clergy-religious-school-coordinator-congregation-ahavath-chesed-the-temple-jacksonville-jacksonville</t>
+  </si>
+  <si>
+    <t>Communications &amp; Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Center for Civic Engagement, Northwestern University</t>
+  </si>
+  <si>
+    <t>Evanston, IL</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57300.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e717ebba1a0c4fb6b6cf0cc71e249c27-communications-operations-coordinator-center-for-civic-engagement-northwestern-university-evanston</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>National Alliance to End Homelessness</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 77200.00 - 115800.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cf9c6d856584d8bb3b2ca4017f584bd-communications-manager-national-alliance-to-end-homelessness-washington</t>
+  </si>
+  <si>
+    <t>Conservation Director</t>
+  </si>
+  <si>
+    <t>Hispanic Access Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ab74a3e4a2249adbdd89f68c7ee4ee3-conservation-director-hispanic-access-foundation-washington</t>
+  </si>
+  <si>
+    <t>Contract Attorney, Children's Program</t>
+  </si>
+  <si>
+    <t>Amica Center for Immigrant Rights (Amica Center)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4910da4196d6497192aa6761763240eb-contract-attorney-childrens-program-amica-center-for-immigrant-rights-amica-center-washington</t>
+  </si>
+  <si>
+    <t>Coordinator, Finance</t>
+  </si>
+  <si>
+    <t>DigDeep</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 26.50 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/324e23cd62064d07872b2fa0632dd6bf-coordinator-finance-digdeep-los-angeles</t>
+  </si>
+  <si>
+    <t>Data Coordinator</t>
+  </si>
+  <si>
+    <t>Political Asylum Immigration Representation Project</t>
+  </si>
+  <si>
+    <t>USD 61500.00 - 67500.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c510aee8bc74cd28e9097cc1480525e-data-coordinator-political-asylum-immigration-representation-project-boston</t>
+  </si>
+  <si>
+    <t>Deputy Chief of Out of School Time</t>
+  </si>
+  <si>
+    <t>Arts for Learning Maryland</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 109000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/364539b683744ef8bc5b70c87d3ca692-deputy-chief-of-out-of-school-time-arts-for-learning-maryland-baltimore</t>
+  </si>
+  <si>
+    <t>Deputy Program Director, Children's Program (DUCs)</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 100100.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/070edb4312c146a89d87d2a557bd8d1a-deputy-program-director-childrens-program-ducs-amica-center-for-immigrant-rights-amica-center-washington</t>
+  </si>
+  <si>
+    <t>Development Manager (Deputy Director of Leadership Giving)</t>
+  </si>
+  <si>
+    <t>Baruch College</t>
+  </si>
+  <si>
+    <t>USD 102460.00 - 113745.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9446db5e6a1e4e7584c4078bc20e142e-development-manager-deputy-director-of-leadership-giving-baruch-college-new-york</t>
+  </si>
+  <si>
+    <t>Development Operations Associate</t>
+  </si>
+  <si>
+    <t>Popular Democracy</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f15d2cbc49a3483b890a895ee63caf66-development-operations-associate-popular-democracy-brooklyn</t>
+  </si>
+  <si>
+    <t>Digital Community Manager</t>
+  </si>
+  <si>
+    <t>Dear Fem’Me</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Sexual Abuse Human Trafficking, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/27b4ebf1d0d24962a1e6761004b913f2-digital-community-manager-dear-femme-osun</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>JustLeadershipUSA</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Crime Safety, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16056a45837443e0b7299a3fd8338c8d-director-of-communications-justleadershipusa-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Abilis</t>
+  </si>
+  <si>
+    <t>GREENWICH, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Economic Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfb12ec4ab0e4e29b08258837d66f4af-director-of-development-abilis-greenwich</t>
+  </si>
+  <si>
+    <t>New Mexico Museum of Natural History Foundation</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>Philanthropy, Science Technology, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9308c98906694a17881f27b88ff10ed6-director-of-development-new-mexico-museum-of-natural-history-foundation-albuquerque</t>
+  </si>
+  <si>
+    <t>Director of Strategic Partnerships, Cradle-to-Career</t>
+  </si>
+  <si>
+    <t>United Way of Central and Northeastern CT</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05f7c562b95b40149d1c8364049bf517-director-of-strategic-partnerships-cradle-to-career-united-way-of-central-and-northeastern-ct-hartford</t>
+  </si>
+  <si>
+    <t>Director, Data &amp; IT</t>
+  </si>
+  <si>
+    <t>EdReports</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 139114.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec620d31c9ea4317bff068d791e9abeb-director-data-it-edreports-raleigh</t>
+  </si>
+  <si>
+    <t>Disability Rights Staff Attorney</t>
+  </si>
+  <si>
+    <t>Disability Rights DC at University Legal Services</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a40a5eb95624af485b58ea794db0daf-disability-rights-staff-attorney-disability-rights-dc-at-university-legal-services-washington</t>
+  </si>
+  <si>
+    <t>Elementary Teacher</t>
+  </si>
+  <si>
+    <t>USD 47250.00 - 54600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f419ae91e00441783c8b67a9eaefdfe-elementary-teacher-intergenerational-schools-cleveland</t>
+  </si>
+  <si>
+    <t>ELIGIBILITY SPECIALIST- METROPOLITAN HOUSING ACCESS PROGRAM (MHAP)</t>
+  </si>
+  <si>
+    <t>Housing Counseling Services, Inc.</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac9e9df8dd9a4eaba819c61c27b1574a-eligibility-specialist-metropolitan-housing-access-program-mhap-housing-counseling-services-inc-washington</t>
+  </si>
+  <si>
+    <t>Evaluation and Monitoring Associate Position</t>
+  </si>
+  <si>
+    <t>Massachusetts Legal Assistance Corporation</t>
+  </si>
+  <si>
+    <t>USD 51800.00 - 69400.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f882517e6575403fa455c70b58f7b8ac-evaluation-and-monitoring-associate-position-massachusetts-legal-assistance-corporation-boston</t>
+  </si>
+  <si>
+    <t>Innocence Project of Texas</t>
+  </si>
+  <si>
+    <t>Fort Worth, Texas</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fcce8a5cc389428e9756eecda47093f4-executive-director-innocence-project-of-texas-fort-worth</t>
+  </si>
+  <si>
+    <t>Economic Hardship Reporting Project</t>
+  </si>
+  <si>
+    <t>USD 135000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d96e3ffb26964fd19b70fc8877ad31b6-executive-director-economic-hardship-reporting-project-brooklyn</t>
+  </si>
+  <si>
+    <t>Extended Care Teacher (Part-time)</t>
+  </si>
+  <si>
+    <t>Hiba Academy Bay Area</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d510050c54644c57be0538572af35f98-extended-care-teacher-part-time-hiba-academy-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Facilitator/Counselor, Bartlett Substance Recovery Service (DOM-Infectious Diseases)</t>
+  </si>
+  <si>
+    <t>Johns Hopkins University</t>
+  </si>
+  <si>
+    <t>USD 17.54 - 30.65/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/186f8123b4404ce4970630c172501f81-facilitatorcounselor-bartlett-substance-recovery-service-dom-infectious-diseases-johns-hopkins-university-baltimore</t>
+  </si>
+  <si>
+    <t>Finance &amp; Development Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Congressional Black Caucus Foundation</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bbfed7756d74bbba355562cb52f6f79-finance-development-operations-coordinator-congressional-black-caucus-foundation-washington</t>
+  </si>
+  <si>
+    <t>Finance Officer</t>
+  </si>
+  <si>
+    <t>Fortify Health</t>
+  </si>
+  <si>
+    <t>Remote (IN)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bec3eb108ab44cec8df12da2f686b5ec-finance-officer-fortify-health-new-delhi</t>
+  </si>
+  <si>
+    <t>Front Office Coordinator</t>
+  </si>
+  <si>
+    <t>Sojourner House Inc.</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Family, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05a61af83d134df795646edc31c5bcc4-front-office-coordinator-sojourner-house-inc-boston</t>
+  </si>
+  <si>
+    <t>HR &amp; Payroll Specialist</t>
+  </si>
+  <si>
+    <t>Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, VA</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a5e0ab51da3482fbf54eaff2651ff78-hr-payroll-specialist-piedmont-environmental-council-warrenton</t>
+  </si>
+  <si>
+    <t>Hub Manager - Cambodia (Kampot)</t>
+  </si>
+  <si>
+    <t>FutureSense Foundation</t>
+  </si>
+  <si>
+    <t>Kampot, Kampot Province, KH</t>
+  </si>
+  <si>
+    <t>USD 800.00 - 1000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87c777e411c54878aeafb63bd5d67343-hub-manager-cambodia-kampot-futuresense-foundation-kampot</t>
+  </si>
+  <si>
+    <t>Human Resources Manager</t>
+  </si>
+  <si>
+    <t>Jewish Community Council of Greater Coney Island</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c6087854e9a426489543088e68e77cc-human-resources-manager-jewish-community-council-of-greater-coney-island-kings-county</t>
+  </si>
+  <si>
+    <t>Intervention Specialist</t>
+  </si>
+  <si>
+    <t>USD 49350.00 - 56700.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a971923fe9224d139b2bdbbc0943e996-intervention-specialist-intergenerational-schools-cleveland</t>
+  </si>
+  <si>
+    <t>Lead Receptionist &amp; Admin Coordinator (Mandarin Speaker)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08ecaebebc984ee69e6d2a0775630dad-lead-receptionist-admin-coordinator-mandarin-speaker-hiba-academy-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Leadership Gift Officer, Graduate School of Arts &amp; Sciences</t>
+  </si>
+  <si>
+    <t>Columbia University, Office of Alumni Relations and Development</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ef63651abbf4c98aace6ffa9e886382-leadership-gift-officer-graduate-school-of-arts-sciences-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
+    <t>Manager of Social Work Supported Programs - Westchester</t>
+  </si>
+  <si>
+    <t>DOROT</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc1f609ffe1844118475686d12bfbc53-manager-of-social-work-supported-programs-westchester-dorot-white-plains</t>
+  </si>
+  <si>
+    <t>Operations and Program Manager</t>
+  </si>
+  <si>
+    <t>Invictus Enterprises Foundation Inc</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac876e1961ee4a85ae6a945104e08ec0-operations-and-program-manager-invictus-enterprises-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Outdoor Education Teacher/Naturalist</t>
+  </si>
+  <si>
+    <t>Echo Hill Outdoor School</t>
+  </si>
+  <si>
+    <t>Worton, Maryland</t>
+  </si>
+  <si>
+    <t>USD 350.00 - 400.00/week</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ed35531cd0e4389a7d3c8167da39bb0-outdoor-education-teachernaturalist-echo-hill-outdoor-school-worton</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>Youth Represent</t>
+  </si>
+  <si>
+    <t>USD 58350.00 - 66629.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce663dc2da4c44d8bc17e4143de731f2-paralegal-youth-represent-new-york</t>
+  </si>
+  <si>
+    <t>Part Time Facilitator</t>
+  </si>
+  <si>
+    <t>Girls Inc. of Long Island</t>
+  </si>
+  <si>
+    <t>Deer Park, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ebcbdb4524e42658cc46d306b716f23-part-time-facilitator-girls-inc-of-long-island-deer-park</t>
+  </si>
+  <si>
+    <t>Part-time Youth Advisor</t>
+  </si>
+  <si>
+    <t>Trinity Church NYC</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/960672ecb99c4b448f60607637e60626-part-time-youth-advisor-trinity-church-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Patient Meal Coordinator</t>
+  </si>
+  <si>
+    <t>Culinary Care</t>
+  </si>
+  <si>
+    <t>Remote (Chicago, Illinois)</t>
+  </si>
+  <si>
+    <t>USD 22.50 - 22.50/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf484e07a6354e598af9673e55798971-patient-meal-coordinator-culinary-care-chicago</t>
+  </si>
+  <si>
+    <t>Politcal Canvasser</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3a9278675704a44938672bbccd9e92e-politcal-canvasser-worker-power-phoenix</t>
+  </si>
+  <si>
+    <t>Casa Grande, Arizona</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e9c425bd3554483a6c4fd2f71fa39b7-politcal-canvasser-worker-power-casa-grande</t>
+  </si>
+  <si>
+    <t>President/CEO</t>
+  </si>
+  <si>
+    <t>Cumberland Community Foundation</t>
+  </si>
+  <si>
+    <t>Fayetteville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 260000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6b6ae673f4364052a996560222d7560a-presidentceo-cumberland-community-foundation-fayetteville</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Downtown Worcester Business Improvement District</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26c864884fef4e5e84e4ebc81ac2638e-program-coordinator-downtown-worcester-business-improvement-district-worcester</t>
+  </si>
+  <si>
+    <t>Program Facilitator, Peer Cohorts (Texas &amp; Arkansas)</t>
+  </si>
+  <si>
+    <t>Nasdaq Entrepreneurial Center</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68113c671aaa427282223ea5fcdcee8b-program-facilitator-peer-cohorts-texas-arkansas-nasdaq-entrepreneurial-center-houston</t>
+  </si>
+  <si>
+    <t>Program Manager, Animal Research Issues</t>
+  </si>
+  <si>
+    <t>Humane World for Animals</t>
+  </si>
+  <si>
+    <t>USD 63400.00 - 95200.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbc43750170c45fcbe7a126af6b5bd33-program-manager-animal-research-issues-humane-world-for-animals-washington</t>
+  </si>
+  <si>
+    <t>Programme Delivery Lead - Thailand</t>
+  </si>
+  <si>
+    <t>Mae Sariang, Mae Hong Son, TH</t>
+  </si>
+  <si>
+    <t>THB 25000.00 - 28000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4a6996f8eec4b4bb5a114ceb2106e67-programme-delivery-lead-thailand-futuresense-foundation-mae-sariang</t>
+  </si>
+  <si>
+    <t>Regional Coordinator, START Center Initiative</t>
+  </si>
+  <si>
+    <t>Big Picture Learning</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 82350.00 - 82350.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/269973e59d8c4bd4b1efdc2d5fe74b61-regional-coordinator-start-center-initiative-big-picture-learning-providence</t>
+  </si>
+  <si>
+    <t>Senior Manager of Events</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2fb6256fd2b545f6b6b03fc94d9dc58c-senior-manager-of-events-powered-by-professionals-new-york</t>
+  </si>
+  <si>
+    <t>Senior Manager, Marketing &amp; Engagement</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/237236e54fb94b71bba57e926dce2f90-senior-manager-marketing-engagement-united-way-of-central-and-northeastern-ct-hartford</t>
+  </si>
+  <si>
+    <t>Senior Regional Manager, Philanthropy</t>
+  </si>
+  <si>
+    <t>Mercy Housing California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0241fbe11c0a43bdbbefacce3ac7e526-senior-regional-manager-philanthropy-mercy-housing-california-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Writer - Institutional Giving</t>
+  </si>
+  <si>
+    <t>Tenacity, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20d8ef52e9754f729cc7a1f4119ed576-senior-writer-institutional-giving-tenacity-inc-boston</t>
+  </si>
+  <si>
+    <t>Social Worker - Community Guardian Program</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>USD 66300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/561988af32044cffbfb87dbc976317c8-social-worker-community-guardian-program-jewish-association-serving-the-aging-new-york</t>
+  </si>
+  <si>
+    <t>Special Events and Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Fenway Community Center at Viridian, Inc.</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/727a46f4f72e4b0ab27dc5c7b6be9ba1-special-events-and-fundraising-manager-fenway-community-center-at-viridian-inc-boston</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Alameda County Homeless Action Center</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 84495.00 - 125555.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/591f8e06b67d4ba8a7790f2a891d9a78-staff-attorney-alameda-county-homeless-action-center-berkeley</t>
+  </si>
+  <si>
+    <t>U Street Main Street Manager</t>
+  </si>
+  <si>
+    <t>District Bridges</t>
+  </si>
+  <si>
+    <t>Community Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58e835e5af3140fd9af5017569327cf8-u-street-main-street-manager-district-bridges-washington</t>
+  </si>
+  <si>
+    <t>Vice President -- National Civic Art Society -- Classical Public Art and Architecture</t>
+  </si>
+  <si>
+    <t>National Civic Art Society</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2ce095104024cbb81ee5704bc93b475-vice-president-national-civic-art-society-classical-public-art-and-architecture-national-civic-art-society-washington</t>
+  </si>
+  <si>
+    <t>VP, Clinical Strategy &amp; Education</t>
+  </si>
+  <si>
+    <t>Living Beyond Breast Cancer</t>
+  </si>
+  <si>
+    <t>Bala Cynwyd, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 140000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/543fc05cc6dc4b729a6107be4c6cd9c4-vp-clinical-strategy-education-living-beyond-breast-cancer-bala-cynwyd</t>
+  </si>
+  <si>
+    <t>Wellbeing Navigator</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 75507.00 - 83897.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f725b8ceebbc4dc9a33ac6090651dfca-wellbeing-navigator-american-speech-language-hearing-association-rockville</t>
   </si>
 </sst>
 </file>
@@ -693,7 +2292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -766,315 +2365,1074 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="H6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+      <c r="H10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
         <v>92</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F18" t="s">
         <v>93</v>
       </c>
-      <c r="C16" t="s">
+      <c r="H18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>95</v>
       </c>
-      <c r="F16" t="s">
+      <c r="B19" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="C19" t="s">
         <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" t="s">
+        <v>201</v>
+      </c>
+      <c r="F38" t="s">
+        <v>202</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>209</v>
+      </c>
+      <c r="F39" t="s">
+        <v>210</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>215</v>
+      </c>
+      <c r="F40" t="s">
+        <v>216</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>218</v>
+      </c>
+      <c r="B41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" t="s">
+        <v>221</v>
+      </c>
+      <c r="F41" t="s">
+        <v>222</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>224</v>
+      </c>
+      <c r="B42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>229</v>
+      </c>
+      <c r="B43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>237</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" t="s">
+        <v>242</v>
+      </c>
+      <c r="F45" t="s">
+        <v>80</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>244</v>
+      </c>
+      <c r="B46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46" t="s">
+        <v>246</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" t="s">
+        <v>248</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>250</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" t="s">
+        <v>202</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>252</v>
+      </c>
+      <c r="B48" t="s">
+        <v>253</v>
+      </c>
+      <c r="C48" t="s">
+        <v>254</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>255</v>
+      </c>
+      <c r="F48" t="s">
+        <v>256</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
+        <v>259</v>
+      </c>
+      <c r="D49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" t="s">
+        <v>260</v>
+      </c>
+      <c r="F49" t="s">
+        <v>261</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -1095,6 +3453,39 @@
     <hyperlink ref="H14" r:id="rId13"/>
     <hyperlink ref="H15" r:id="rId14"/>
     <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1151,7 +3542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1190,8 +3581,1786 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F6" t="s">
+        <v>290</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C9" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" t="s">
+        <v>307</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" t="s">
+        <v>313</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F11" t="s">
+        <v>320</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C13" t="s">
+        <v>278</v>
+      </c>
+      <c r="D13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F13" t="s">
+        <v>331</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>333</v>
+      </c>
+      <c r="B14" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" t="s">
+        <v>337</v>
+      </c>
+      <c r="F14" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" t="s">
+        <v>344</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" t="s">
+        <v>290</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" t="s">
+        <v>352</v>
+      </c>
+      <c r="C17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F17" t="s">
+        <v>355</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>357</v>
+      </c>
+      <c r="B18" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" t="s">
+        <v>359</v>
+      </c>
+      <c r="D18" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" t="s">
+        <v>360</v>
+      </c>
+      <c r="F18" t="s">
+        <v>361</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B19" t="s">
+        <v>364</v>
+      </c>
+      <c r="C19" t="s">
+        <v>365</v>
+      </c>
+      <c r="D19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" t="s">
+        <v>366</v>
+      </c>
+      <c r="F19" t="s">
+        <v>367</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B20" t="s">
+        <v>370</v>
+      </c>
+      <c r="C20" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" t="s">
+        <v>290</v>
+      </c>
+      <c r="F20" t="s">
+        <v>290</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>372</v>
+      </c>
+      <c r="B21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E21" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" t="s">
+        <v>376</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" t="s">
+        <v>379</v>
+      </c>
+      <c r="C22" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E22" t="s">
+        <v>380</v>
+      </c>
+      <c r="F22" t="s">
+        <v>381</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>383</v>
+      </c>
+      <c r="B23" t="s">
+        <v>384</v>
+      </c>
+      <c r="C23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D23" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" t="s">
+        <v>386</v>
+      </c>
+      <c r="F23" t="s">
+        <v>387</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>389</v>
+      </c>
+      <c r="B24" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" t="s">
+        <v>359</v>
+      </c>
+      <c r="D24" t="s">
+        <v>266</v>
+      </c>
+      <c r="E24" t="s">
+        <v>390</v>
+      </c>
+      <c r="F24" t="s">
+        <v>290</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C25" t="s">
+        <v>278</v>
+      </c>
+      <c r="D25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" t="s">
+        <v>394</v>
+      </c>
+      <c r="F25" t="s">
+        <v>290</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>396</v>
+      </c>
+      <c r="B26" t="s">
+        <v>397</v>
+      </c>
+      <c r="C26" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" t="s">
+        <v>398</v>
+      </c>
+      <c r="F26" t="s">
+        <v>399</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" t="s">
+        <v>402</v>
+      </c>
+      <c r="C27" t="s">
+        <v>365</v>
+      </c>
+      <c r="D27" t="s">
+        <v>336</v>
+      </c>
+      <c r="E27" t="s">
+        <v>290</v>
+      </c>
+      <c r="F27" t="s">
+        <v>403</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>405</v>
+      </c>
+      <c r="B28" t="s">
+        <v>406</v>
+      </c>
+      <c r="C28" t="s">
+        <v>365</v>
+      </c>
+      <c r="D28" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" t="s">
+        <v>407</v>
+      </c>
+      <c r="F28" t="s">
+        <v>408</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>410</v>
+      </c>
+      <c r="B29" t="s">
+        <v>411</v>
+      </c>
+      <c r="C29" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F29" t="s">
+        <v>414</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B30" t="s">
+        <v>416</v>
+      </c>
+      <c r="C30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D30" t="s">
+        <v>266</v>
+      </c>
+      <c r="E30" t="s">
+        <v>290</v>
+      </c>
+      <c r="F30" t="s">
+        <v>418</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>420</v>
+      </c>
+      <c r="B31" t="s">
+        <v>421</v>
+      </c>
+      <c r="C31" t="s">
+        <v>342</v>
+      </c>
+      <c r="D31" t="s">
+        <v>266</v>
+      </c>
+      <c r="E31" t="s">
+        <v>422</v>
+      </c>
+      <c r="F31" t="s">
+        <v>423</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>425</v>
+      </c>
+      <c r="B32" t="s">
+        <v>426</v>
+      </c>
+      <c r="C32" t="s">
+        <v>365</v>
+      </c>
+      <c r="D32" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" t="s">
+        <v>427</v>
+      </c>
+      <c r="F32" t="s">
+        <v>428</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>430</v>
+      </c>
+      <c r="B33" t="s">
+        <v>431</v>
+      </c>
+      <c r="C33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" t="s">
+        <v>266</v>
+      </c>
+      <c r="E33" t="s">
+        <v>398</v>
+      </c>
+      <c r="F33" t="s">
+        <v>432</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>434</v>
+      </c>
+      <c r="B34" t="s">
+        <v>323</v>
+      </c>
+      <c r="C34" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" t="s">
+        <v>266</v>
+      </c>
+      <c r="E34" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" t="s">
+        <v>326</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>437</v>
+      </c>
+      <c r="B35" t="s">
+        <v>438</v>
+      </c>
+      <c r="C35" t="s">
+        <v>359</v>
+      </c>
+      <c r="D35" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" t="s">
+        <v>312</v>
+      </c>
+      <c r="F35" t="s">
+        <v>439</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>441</v>
+      </c>
+      <c r="B36" t="s">
+        <v>442</v>
+      </c>
+      <c r="C36" t="s">
+        <v>272</v>
+      </c>
+      <c r="D36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E36" t="s">
+        <v>443</v>
+      </c>
+      <c r="F36" t="s">
+        <v>444</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" t="s">
+        <v>446</v>
+      </c>
+      <c r="C37" t="s">
+        <v>447</v>
+      </c>
+      <c r="D37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" t="s">
+        <v>290</v>
+      </c>
+      <c r="F37" t="s">
+        <v>448</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" t="s">
+        <v>365</v>
+      </c>
+      <c r="D38" t="s">
+        <v>266</v>
+      </c>
+      <c r="E38" t="s">
+        <v>451</v>
+      </c>
+      <c r="F38" t="s">
+        <v>452</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>454</v>
+      </c>
+      <c r="B39" t="s">
+        <v>455</v>
+      </c>
+      <c r="C39" t="s">
+        <v>300</v>
+      </c>
+      <c r="D39" t="s">
+        <v>336</v>
+      </c>
+      <c r="E39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F39" t="s">
+        <v>457</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>459</v>
+      </c>
+      <c r="B40" t="s">
+        <v>460</v>
+      </c>
+      <c r="C40" t="s">
+        <v>385</v>
+      </c>
+      <c r="D40" t="s">
+        <v>266</v>
+      </c>
+      <c r="E40" t="s">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>428</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>463</v>
+      </c>
+      <c r="B41" t="s">
+        <v>464</v>
+      </c>
+      <c r="C41" t="s">
+        <v>359</v>
+      </c>
+      <c r="D41" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41" t="s">
+        <v>465</v>
+      </c>
+      <c r="F41" t="s">
+        <v>466</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>468</v>
+      </c>
+      <c r="B42" t="s">
+        <v>469</v>
+      </c>
+      <c r="C42" t="s">
+        <v>470</v>
+      </c>
+      <c r="D42" t="s">
+        <v>471</v>
+      </c>
+      <c r="E42" t="s">
+        <v>290</v>
+      </c>
+      <c r="F42" t="s">
+        <v>472</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>474</v>
+      </c>
+      <c r="B43" t="s">
+        <v>475</v>
+      </c>
+      <c r="C43" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" t="s">
+        <v>266</v>
+      </c>
+      <c r="E43" t="s">
+        <v>476</v>
+      </c>
+      <c r="F43" t="s">
+        <v>477</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>479</v>
+      </c>
+      <c r="B44" t="s">
+        <v>480</v>
+      </c>
+      <c r="C44" t="s">
+        <v>481</v>
+      </c>
+      <c r="D44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>482</v>
+      </c>
+      <c r="F44" t="s">
+        <v>483</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>485</v>
+      </c>
+      <c r="B45" t="s">
+        <v>486</v>
+      </c>
+      <c r="C45" t="s">
+        <v>487</v>
+      </c>
+      <c r="D45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E45" t="s">
+        <v>488</v>
+      </c>
+      <c r="F45" t="s">
+        <v>489</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>491</v>
+      </c>
+      <c r="B46" t="s">
+        <v>492</v>
+      </c>
+      <c r="C46" t="s">
+        <v>493</v>
+      </c>
+      <c r="D46" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" t="s">
+        <v>306</v>
+      </c>
+      <c r="F46" t="s">
+        <v>326</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>495</v>
+      </c>
+      <c r="B47" t="s">
+        <v>323</v>
+      </c>
+      <c r="C47" t="s">
+        <v>324</v>
+      </c>
+      <c r="D47" t="s">
+        <v>266</v>
+      </c>
+      <c r="E47" t="s">
+        <v>496</v>
+      </c>
+      <c r="F47" t="s">
+        <v>326</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>498</v>
+      </c>
+      <c r="B48" t="s">
+        <v>455</v>
+      </c>
+      <c r="C48" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" t="s">
+        <v>266</v>
+      </c>
+      <c r="E48" t="s">
+        <v>499</v>
+      </c>
+      <c r="F48" t="s">
+        <v>457</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>501</v>
+      </c>
+      <c r="B49" t="s">
+        <v>502</v>
+      </c>
+      <c r="C49" t="s">
+        <v>278</v>
+      </c>
+      <c r="D49" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" t="s">
+        <v>503</v>
+      </c>
+      <c r="F49" t="s">
+        <v>290</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>505</v>
+      </c>
+      <c r="B50" t="s">
+        <v>506</v>
+      </c>
+      <c r="C50" t="s">
+        <v>507</v>
+      </c>
+      <c r="D50" t="s">
+        <v>266</v>
+      </c>
+      <c r="E50" t="s">
+        <v>508</v>
+      </c>
+      <c r="F50" t="s">
+        <v>509</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>511</v>
+      </c>
+      <c r="B51" t="s">
+        <v>512</v>
+      </c>
+      <c r="C51" t="s">
+        <v>278</v>
+      </c>
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" t="s">
+        <v>513</v>
+      </c>
+      <c r="F51" t="s">
+        <v>290</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>515</v>
+      </c>
+      <c r="B52" t="s">
+        <v>516</v>
+      </c>
+      <c r="C52" t="s">
+        <v>517</v>
+      </c>
+      <c r="D52" t="s">
+        <v>318</v>
+      </c>
+      <c r="E52" t="s">
+        <v>518</v>
+      </c>
+      <c r="F52" t="s">
+        <v>519</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>521</v>
+      </c>
+      <c r="B53" t="s">
+        <v>522</v>
+      </c>
+      <c r="C53" t="s">
+        <v>278</v>
+      </c>
+      <c r="D53" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" t="s">
+        <v>523</v>
+      </c>
+      <c r="F53" t="s">
+        <v>524</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>526</v>
+      </c>
+      <c r="B54" t="s">
+        <v>527</v>
+      </c>
+      <c r="C54" t="s">
+        <v>528</v>
+      </c>
+      <c r="D54" t="s">
+        <v>336</v>
+      </c>
+      <c r="E54" t="s">
+        <v>529</v>
+      </c>
+      <c r="F54" t="s">
+        <v>326</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>531</v>
+      </c>
+      <c r="B55" t="s">
+        <v>532</v>
+      </c>
+      <c r="C55" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" t="s">
+        <v>336</v>
+      </c>
+      <c r="E55" t="s">
+        <v>533</v>
+      </c>
+      <c r="F55" t="s">
+        <v>290</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>535</v>
+      </c>
+      <c r="B56" t="s">
+        <v>536</v>
+      </c>
+      <c r="C56" t="s">
+        <v>537</v>
+      </c>
+      <c r="D56" t="s">
+        <v>336</v>
+      </c>
+      <c r="E56" t="s">
+        <v>538</v>
+      </c>
+      <c r="F56" t="s">
+        <v>539</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>541</v>
+      </c>
+      <c r="B57" t="s">
+        <v>542</v>
+      </c>
+      <c r="C57" t="s">
+        <v>543</v>
+      </c>
+      <c r="D57" t="s">
+        <v>318</v>
+      </c>
+      <c r="E57" t="s">
+        <v>544</v>
+      </c>
+      <c r="F57" t="s">
+        <v>545</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>541</v>
+      </c>
+      <c r="B58" t="s">
+        <v>542</v>
+      </c>
+      <c r="C58" t="s">
+        <v>547</v>
+      </c>
+      <c r="D58" t="s">
+        <v>318</v>
+      </c>
+      <c r="E58" t="s">
+        <v>544</v>
+      </c>
+      <c r="F58" t="s">
+        <v>545</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>549</v>
+      </c>
+      <c r="B59" t="s">
+        <v>550</v>
+      </c>
+      <c r="C59" t="s">
+        <v>551</v>
+      </c>
+      <c r="D59" t="s">
+        <v>266</v>
+      </c>
+      <c r="E59" t="s">
+        <v>552</v>
+      </c>
+      <c r="F59" t="s">
+        <v>290</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>554</v>
+      </c>
+      <c r="B60" t="s">
+        <v>555</v>
+      </c>
+      <c r="C60" t="s">
+        <v>556</v>
+      </c>
+      <c r="D60" t="s">
+        <v>266</v>
+      </c>
+      <c r="E60" t="s">
+        <v>557</v>
+      </c>
+      <c r="F60" t="s">
+        <v>558</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>560</v>
+      </c>
+      <c r="B61" t="s">
+        <v>561</v>
+      </c>
+      <c r="C61" t="s">
+        <v>562</v>
+      </c>
+      <c r="D61" t="s">
+        <v>266</v>
+      </c>
+      <c r="E61" t="s">
+        <v>563</v>
+      </c>
+      <c r="F61" t="s">
+        <v>564</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>566</v>
+      </c>
+      <c r="B62" t="s">
+        <v>567</v>
+      </c>
+      <c r="C62" t="s">
+        <v>359</v>
+      </c>
+      <c r="D62" t="s">
+        <v>266</v>
+      </c>
+      <c r="E62" t="s">
+        <v>568</v>
+      </c>
+      <c r="F62" t="s">
+        <v>569</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>571</v>
+      </c>
+      <c r="B63" t="s">
+        <v>486</v>
+      </c>
+      <c r="C63" t="s">
+        <v>572</v>
+      </c>
+      <c r="D63" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" t="s">
+        <v>573</v>
+      </c>
+      <c r="F63" t="s">
+        <v>489</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>575</v>
+      </c>
+      <c r="B64" t="s">
+        <v>576</v>
+      </c>
+      <c r="C64" t="s">
+        <v>577</v>
+      </c>
+      <c r="D64" t="s">
+        <v>266</v>
+      </c>
+      <c r="E64" t="s">
+        <v>578</v>
+      </c>
+      <c r="F64" t="s">
+        <v>326</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>580</v>
+      </c>
+      <c r="B65" t="s">
+        <v>305</v>
+      </c>
+      <c r="C65" t="s">
+        <v>278</v>
+      </c>
+      <c r="D65" t="s">
+        <v>266</v>
+      </c>
+      <c r="E65" t="s">
+        <v>581</v>
+      </c>
+      <c r="F65" t="s">
+        <v>307</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>583</v>
+      </c>
+      <c r="B66" t="s">
+        <v>421</v>
+      </c>
+      <c r="C66" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" t="s">
+        <v>584</v>
+      </c>
+      <c r="F66" t="s">
+        <v>585</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>587</v>
+      </c>
+      <c r="B67" t="s">
+        <v>588</v>
+      </c>
+      <c r="C67" t="s">
+        <v>374</v>
+      </c>
+      <c r="D67" t="s">
+        <v>266</v>
+      </c>
+      <c r="E67" t="s">
+        <v>366</v>
+      </c>
+      <c r="F67" t="s">
+        <v>290</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>590</v>
+      </c>
+      <c r="B68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C68" t="s">
+        <v>592</v>
+      </c>
+      <c r="D68" t="s">
+        <v>266</v>
+      </c>
+      <c r="E68" t="s">
+        <v>593</v>
+      </c>
+      <c r="F68" t="s">
+        <v>594</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>596</v>
+      </c>
+      <c r="B69" t="s">
+        <v>597</v>
+      </c>
+      <c r="C69" t="s">
+        <v>278</v>
+      </c>
+      <c r="D69" t="s">
+        <v>266</v>
+      </c>
+      <c r="E69" t="s">
+        <v>598</v>
+      </c>
+      <c r="F69" t="s">
+        <v>290</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>600</v>
+      </c>
+      <c r="B70" t="s">
+        <v>601</v>
+      </c>
+      <c r="C70" t="s">
+        <v>592</v>
+      </c>
+      <c r="D70" t="s">
+        <v>336</v>
+      </c>
+      <c r="E70" t="s">
+        <v>529</v>
+      </c>
+      <c r="F70" t="s">
+        <v>602</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>604</v>
+      </c>
+      <c r="B71" t="s">
+        <v>605</v>
+      </c>
+      <c r="C71" t="s">
+        <v>606</v>
+      </c>
+      <c r="D71" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" t="s">
+        <v>607</v>
+      </c>
+      <c r="F71" t="s">
+        <v>608</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>610</v>
+      </c>
+      <c r="B72" t="s">
+        <v>611</v>
+      </c>
+      <c r="C72" t="s">
+        <v>359</v>
+      </c>
+      <c r="D72" t="s">
+        <v>266</v>
+      </c>
+      <c r="E72" t="s">
+        <v>398</v>
+      </c>
+      <c r="F72" t="s">
+        <v>612</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>614</v>
+      </c>
+      <c r="B73" t="s">
+        <v>615</v>
+      </c>
+      <c r="C73" t="s">
+        <v>365</v>
+      </c>
+      <c r="D73" t="s">
+        <v>266</v>
+      </c>
+      <c r="E73" t="s">
+        <v>616</v>
+      </c>
+      <c r="F73" t="s">
+        <v>617</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>619</v>
+      </c>
+      <c r="B74" t="s">
+        <v>620</v>
+      </c>
+      <c r="C74" t="s">
+        <v>621</v>
+      </c>
+      <c r="D74" t="s">
+        <v>266</v>
+      </c>
+      <c r="E74" t="s">
+        <v>622</v>
+      </c>
+      <c r="F74" t="s">
+        <v>623</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>625</v>
+      </c>
+      <c r="B75" t="s">
+        <v>626</v>
+      </c>
+      <c r="C75" t="s">
+        <v>627</v>
+      </c>
+      <c r="D75" t="s">
+        <v>266</v>
+      </c>
+      <c r="E75" t="s">
+        <v>628</v>
+      </c>
+      <c r="F75" t="s">
+        <v>629</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-15.xlsx
+++ b/docs/xlsx/jobs-2026-10-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="934">
   <si>
     <t>Title</t>
   </si>
@@ -805,6 +805,24 @@
     <t>https://www.conservationjobboard.com/job-listing-youth-crew-leader-bozeman-or-kalispell-montana/3230009045</t>
   </si>
   <si>
+    <t>Property Management Specialist I/II</t>
+  </si>
+  <si>
+    <t>Los Altos, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Land Use</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/property-management-specialist-i-ii-2/</t>
+  </si>
+  <si>
     <t>Accounting and Grants Coordinator</t>
   </si>
   <si>
@@ -844,6 +862,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ed3960128b614e3980da46d6342f25c1-administrative-and-program-associate-league-of-women-voters-of-massachusetts-boston</t>
   </si>
   <si>
+    <t>Advising and Coaching Partnership Manager</t>
+  </si>
+  <si>
+    <t>Michigan College Access Network</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>USD 77400.00 - 77400.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b465e5e646af46d285afd062bb23f066-advising-and-coaching-partnership-manager-michigan-college-access-network-lansing</t>
+  </si>
+  <si>
     <t>Afterschool Program Coordinator</t>
   </si>
   <si>
@@ -886,12 +922,45 @@
     <t>USD 91506.00 - 190644.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/government-job/5724f197546644ce81473e5cbca9d183-assistant-attorney-general-taxpayer-protection-bureau3918-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Assistant Teacher (Guide)</t>
+  </si>
+  <si>
+    <t>Inkwell Montessori</t>
+  </si>
+  <si>
+    <t>Somerville, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Communications Access, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39bb3604b481446ca8836ab98a71a7b1-assistant-teacher-guide-inkwell-montessori-somerville</t>
+  </si>
+  <si>
+    <t>Associate Director of Corporations &amp; Foundations</t>
+  </si>
+  <si>
+    <t>Hunter College Foundation</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d41759997c104146bbb9d5075526d388-associate-director-of-corporations-foundations-hunter-college-foundation-new-york</t>
+  </si>
+  <si>
     <t>Associate Director of Development</t>
   </si>
   <si>
@@ -1000,6 +1069,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/d501e3999e63407489932db7e9496ef3-building-substitute-teacher-intergenerational-schools-cleveland</t>
   </si>
   <si>
+    <t>Tucson Shutdown, a project of the National Institute for Peer Supprt</t>
+  </si>
+  <si>
+    <t>Tucson, Arizona</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 10000.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bf47df907844f6eb70f32a07d510020-campaign-manager-tucson-shutdown-a-project-of-the-national-institute-for-peer-supprt-tucson</t>
+  </si>
+  <si>
+    <t>Canvass Director</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 53750.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed39a9a5663743c4b9d24ddd05561d96-canvass-director-environment-america-minneapolis</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd3f7d00a3064949923cde1deff85bfa-canvass-director-environment-america-philadelphia</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b10b576274ec412fb55692cfbf7e2961-canvass-director-environment-america-denver</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b006c81fb0a64571af8d6d04502f7e77-canvass-director-environment-america-oakland</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a80014a9cfa245bfb7392cb1d766ee8b-canvass-director-environment-america-santa-cruz</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a30b82f678644e658075a1ca5d14b0a2-canvass-director-environment-america-portland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d9e54e402c244fa843caa4a280cb432-canvass-director-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30e6286dde99418197ce834f3d6373c6-canvass-director-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bddc6b40c524beeaef846c7db9a1f62-canvass-director-environment-america-chicago</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b9caf570779471bac2f7696faa55a5c-canvass-director-environment-america-seattle</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -1015,6 +1171,21 @@
     <t>https://www.idealist.org/en/business-job/5bf7b21bf0584829b12db3271c5b1336-case-manager-future-centered-care-new-york</t>
   </si>
   <si>
+    <t>Foothill Unity Center, Inc.</t>
+  </si>
+  <si>
+    <t>Monrovia, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 73840.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba730345ae2c4d969aec49b460ab4a5e-case-manager-foothill-unity-center-inc-monrovia</t>
+  </si>
+  <si>
     <t>Case Manager (Part-Time)</t>
   </si>
   <si>
@@ -1054,6 +1225,15 @@
     <t>https://www.idealist.org/en/consultant-job/2c76823b1d9b4efd9d38b4a521628d69-chief-development-officer-ampersand-consulting-new-england-hartford</t>
   </si>
   <si>
+    <t>Clean Water and Conservation Organizer</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83360b86394f4ca4898b189e6b0453fe-clean-water-and-conservation-organizer-environment-america-philadelphia</t>
+  </si>
+  <si>
     <t>Clergy &amp; Religious School Coordinator</t>
   </si>
   <si>
@@ -1069,6 +1249,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/23eaa08243f4455eabe43dcd410e4096-clergy-religious-school-coordinator-congregation-ahavath-chesed-the-temple-jacksonville-jacksonville</t>
   </si>
   <si>
+    <t>Clinical Forensic Specialist - CAC, Queens</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>USD 30.49 - 34.31/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/424b5b3a0ddf4bd2b0326f94130084aa-clinical-forensic-specialist-cac-queens-safe-horizon-queens</t>
+  </si>
+  <si>
+    <t>Clinical Forensic Specialist - Manhattan CAC</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba1dab9d0e204d8383574f7b6aa5fe85-clinical-forensic-specialist-manhattan-cac-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Therapist</t>
+  </si>
+  <si>
+    <t>Wellness Transformed</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d42d87166c04b36b6dac4a0c0b548f0-clinical-therapist-wellness-transformed-chicago</t>
+  </si>
+  <si>
     <t>Communications &amp; Operations Coordinator</t>
   </si>
   <si>
@@ -1093,9 +1315,6 @@
     <t>National Alliance to End Homelessness</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 77200.00 - 115800.00/year</t>
   </si>
   <si>
@@ -1105,6 +1324,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4cf9c6d856584d8bb3b2ca4017f584bd-communications-manager-national-alliance-to-end-homelessness-washington</t>
   </si>
   <si>
+    <t>Solar One</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee4a6924227045c1981c61c2a759810b-communications-manager-solar-one-queens-county</t>
+  </si>
+  <si>
     <t>Conservation Director</t>
   </si>
   <si>
@@ -1132,6 +1366,21 @@
     <t>https://www.idealist.org/en/job/4910da4196d6497192aa6761763240eb-contract-attorney-childrens-program-amica-center-for-immigrant-rights-amica-center-washington</t>
   </si>
   <si>
+    <t>Contract Storyteller &amp; Newsletter Writer</t>
+  </si>
+  <si>
+    <t>Neighborhood Food Project</t>
+  </si>
+  <si>
+    <t>USD 1200.00 - 1200.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/956a3242a25647bf9133f9dea3947f08-contract-storyteller-newsletter-writer-neighborhood-food-project-ashland</t>
+  </si>
+  <si>
     <t>Coordinator, Finance</t>
   </si>
   <si>
@@ -1150,6 +1399,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/324e23cd62064d07872b2fa0632dd6bf-coordinator-finance-digdeep-los-angeles</t>
   </si>
   <si>
+    <t>CTA &amp; Housing Coordinator</t>
+  </si>
+  <si>
+    <t>National Network to End Domestic Violence</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ffa96d93cc847fe94b32a5208a47a35-cta-housing-coordinator-national-network-to-end-domestic-violence-washington</t>
+  </si>
+  <si>
     <t>Data Coordinator</t>
   </si>
   <si>
@@ -1183,6 +1447,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/364539b683744ef8bc5b70c87d3ca692-deputy-chief-of-out-of-school-time-arts-for-learning-maryland-baltimore</t>
   </si>
   <si>
+    <t>Deputy Program Director, Children's Program</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/070edb4312c146a89d87d2a557bd8d1a-deputy-program-director-childrens-program-amica-center-for-immigrant-rights-amica-center-washington</t>
+  </si>
+  <si>
     <t>Deputy Program Director, Children's Program (DUCs)</t>
   </si>
   <si>
@@ -1276,6 +1546,63 @@
     <t>https://www.idealist.org/en/nonprofit-job/9308c98906694a17881f27b88ff10ed6-director-of-development-new-mexico-museum-of-natural-history-foundation-albuquerque</t>
   </si>
   <si>
+    <t>ZGiRLS Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84e41c0db7674d089738c56ac42eed6e-director-of-development-zgirls-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Oakland Public Education Fund</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8fdff8e4bb44175a1d39113c3bc88d6-director-of-development-oakland-public-education-fund-oakland</t>
+  </si>
+  <si>
+    <t>Director of HR &amp; Administration</t>
+  </si>
+  <si>
+    <t>Equality California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f924a1c464144850a5547128f5b75be4-director-of-hr-administration-equality-california-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>Kesem National</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 126000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbb6d3a84349422da72be6fb8e4a56f3-director-of-philanthropy-kesem-national-covina</t>
+  </si>
+  <si>
     <t>Director of Strategic Partnerships, Cradle-to-Career</t>
   </si>
   <si>
@@ -1300,9 +1627,6 @@
     <t>USD 120000.00 - 139114.00/year</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/ec620d31c9ea4317bff068d791e9abeb-director-data-it-edreports-raleigh</t>
   </si>
   <si>
@@ -1318,6 +1642,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/6a40a5eb95624af485b58ea794db0daf-disability-rights-staff-attorney-disability-rights-dc-at-university-legal-services-washington</t>
   </si>
   <si>
+    <t>East Africa Programme Officer</t>
+  </si>
+  <si>
+    <t>International Detention Coalition</t>
+  </si>
+  <si>
+    <t>Remote (ET)</t>
+  </si>
+  <si>
+    <t>ETB 2093000.00 - 2898000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86acc930032e404c8336379138e40796-east-africa-programme-officer-international-detention-coalition-addis-ababa</t>
+  </si>
+  <si>
+    <t>Economic Justice Campaign Coordinator</t>
+  </si>
+  <si>
+    <t>ALIGN: The Alliance for a Greater New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 77500.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9b4795a271a4d5fba3a865f58bc49e0-economic-justice-campaign-coordinator-align-the-alliance-for-a-greater-new-york-new-york</t>
+  </si>
+  <si>
     <t>Elementary Teacher</t>
   </si>
   <si>
@@ -1354,6 +1711,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/f882517e6575403fa455c70b58f7b8ac-evaluation-and-monitoring-associate-position-massachusetts-legal-assistance-corporation-boston</t>
   </si>
   <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>National Domestic Workers Alliance / La Alianza Nacional de Trabajadores del Hogar</t>
+  </si>
+  <si>
+    <t>USD 66950.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b01435097a8f485aac13eea8e3346076-executive-assistant-national-domestic-workers-alliance-la-alianza-nacional-de-trabajadores-del-hogar-new-york</t>
+  </si>
+  <si>
+    <t>Executive Business Partner, US</t>
+  </si>
+  <si>
+    <t>Regulatory Assistance Project</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/017a18b95b244bdc9bdca920b13ed7a5-executive-business-partner-us-regulatory-assistance-project-montpelier</t>
+  </si>
+  <si>
     <t>Innocence Project of Texas</t>
   </si>
   <si>
@@ -1378,6 +1765,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/d96e3ffb26964fd19b70fc8877ad31b6-executive-director-economic-hardship-reporting-project-brooklyn</t>
   </si>
   <si>
+    <t>The Common Acre</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4ce2fa52bf2410d998574b13ae407de-executive-director-the-common-acre-seattle</t>
+  </si>
+  <si>
+    <t>Executive Director of a small nonprofit that helps homeless students graduate from high school</t>
+  </si>
+  <si>
+    <t>Level Pathways Inc</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f30eac9f38e149578e01225163d06926-executive-director-of-a-small-nonprofit-that-helps-homeless-students-graduate-from-high-school-level-pathways-inc-dallas</t>
+  </si>
+  <si>
     <t>Extended Care Teacher (Part-time)</t>
   </si>
   <si>
@@ -1405,6 +1819,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/186f8123b4404ce4970630c172501f81-facilitatorcounselor-bartlett-substance-recovery-service-dom-infectious-diseases-johns-hopkins-university-baltimore</t>
   </si>
   <si>
+    <t>Federal Environmental Campaigns Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/558dfaf95554428297757844c8c77346-federal-environmental-campaigns-associate-environment-america-washington</t>
+  </si>
+  <si>
     <t>Finance &amp; Development Operations Coordinator</t>
   </si>
   <si>
@@ -1429,15 +1849,24 @@
     <t>Remote (IN)</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>Children Youth, Women</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bec3eb108ab44cec8df12da2f686b5ec-finance-officer-fortify-health-new-delhi</t>
   </si>
   <si>
+    <t>Fiscal Coordinator</t>
+  </si>
+  <si>
+    <t>Grand Street Settlement</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fee18add0f854e98a2b320fea3e11a1c-fiscal-coordinator-grand-street-settlement-new-york</t>
+  </si>
+  <si>
     <t>Front Office Coordinator</t>
   </si>
   <si>
@@ -1453,6 +1882,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/05a61af83d134df795646edc31c5bcc4-front-office-coordinator-sojourner-house-inc-boston</t>
   </si>
   <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Israel Policy Forum</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a54767c0b73c4d92a2f10478750354cb-grants-manager-israel-policy-forum-new-york</t>
+  </si>
+  <si>
+    <t>HOUSING CASE MANAGER</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea12500410f94398b3135a9da0c301a7-housing-case-manager-housing-counseling-services-inc-washington</t>
+  </si>
+  <si>
     <t>HR &amp; Payroll Specialist</t>
   </si>
   <si>
@@ -1489,6 +1942,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/87c777e411c54878aeafb63bd5d67343-hub-manager-cambodia-kampot-futuresense-foundation-kampot</t>
   </si>
   <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>Legal Services Corporation</t>
+  </si>
+  <si>
+    <t>USD 85709.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Civic Engagement, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c26dd36026184670bba06f7a04cc146b-human-resources-generalist-legal-services-corporation-washington</t>
+  </si>
+  <si>
     <t>Human Resources Manager</t>
   </si>
   <si>
@@ -1501,6 +1969,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/1c6087854e9a426489543088e68e77cc-human-resources-manager-jewish-community-council-of-greater-coney-island-kings-county</t>
   </si>
   <si>
+    <t>Immigration Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 105500.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e79b4e19fc5042e8b7e3698ef98233b4-immigration-supervising-attorney-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>Instructional Coach</t>
+  </si>
+  <si>
+    <t>City Teaching Alliance</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 77393.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc878c40fcaf4a028fad870e0f179a0f-instructional-coach-city-teaching-alliance-washington</t>
+  </si>
+  <si>
     <t>Intervention Specialist</t>
   </si>
   <si>
@@ -1510,12 +2008,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/a971923fe9224d139b2bdbbc0943e996-intervention-specialist-intergenerational-schools-cleveland</t>
   </si>
   <si>
+    <t>Junior Staff Accountant</t>
+  </si>
+  <si>
+    <t>Symphony Space</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d4595ad06a24658b6e9a11f2cfbaad2-junior-staff-accountant-symphony-space-new-york</t>
+  </si>
+  <si>
+    <t>Lead Arborist</t>
+  </si>
+  <si>
+    <t>Seattle Botanic Gardens</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a855bbc12dd5433a9c9a4327f8381f77-lead-arborist-seattle-botanic-gardens-seattle</t>
+  </si>
+  <si>
+    <t>Lead Organizer (Full-Time, Exempt)</t>
+  </si>
+  <si>
+    <t>PACT- People Acting in Community Together</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/419c774046c740fbbafd629699c31934-lead-organizer-full-time-exempt-pact-people-acting-in-community-together-san-jose</t>
+  </si>
+  <si>
     <t>Lead Receptionist &amp; Admin Coordinator (Mandarin Speaker)</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/08ecaebebc984ee69e6d2a0775630dad-lead-receptionist-admin-coordinator-mandarin-speaker-hiba-academy-bay-area-san-francisco</t>
   </si>
   <si>
@@ -1531,6 +2068,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5ef63651abbf4c98aace6ffa9e886382-leadership-gift-officer-graduate-school-of-arts-sciences-columbia-university-office-of-alumni-relations-and-development-new-york</t>
   </si>
   <si>
+    <t>Loyal Donor Officer, Gift Planning</t>
+  </si>
+  <si>
+    <t>Partners In Health</t>
+  </si>
+  <si>
+    <t>USD 84460.00 - 90640.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55611d4f21184476aeb82b03d0418752-loyal-donor-officer-gift-planning-partners-in-health-boston</t>
+  </si>
+  <si>
     <t>Manager of Social Work Supported Programs - Westchester</t>
   </si>
   <si>
@@ -1549,6 +2098,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/fc1f609ffe1844118475686d12bfbc53-manager-of-social-work-supported-programs-westchester-dorot-white-plains</t>
   </si>
   <si>
+    <t>Manager, Mission Advancement</t>
+  </si>
+  <si>
+    <t>Best Buddies International Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Richmond, Virginia)</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e3e1c97866a4f60a6fbe51e473b0988-manager-mission-advancement-best-buddies-international-inc-richmond</t>
+  </si>
+  <si>
+    <t>Managing Attorney, Children's Program</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 118250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cd99cef7fd3c4a90b0cde95652bc7bec-managing-attorney-childrens-program-amica-center-for-immigrant-rights-amica-center-washington</t>
+  </si>
+  <si>
+    <t>Mobilizers</t>
+  </si>
+  <si>
+    <t>USD 1000.00 - 1000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d2c954f5e8b4b069d5796aeed82642e-mobilizers-tucson-shutdown-a-project-of-the-national-institute-for-peer-supprt-tucson</t>
+  </si>
+  <si>
     <t>Operations and Program Manager</t>
   </si>
   <si>
@@ -1561,6 +2146,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/ac876e1961ee4a85ae6a945104e08ec0-operations-and-program-manager-invictus-enterprises-foundation-inc-new-york</t>
   </si>
   <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>The Climate Museum</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6df5769ce11a47fdaa0f8e57017bc305-operations-coordinator-the-climate-museum-new-york</t>
+  </si>
+  <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe697013cb334278acaaee00a2b1aeae-organizer-tucson-shutdown-a-project-of-the-national-institute-for-peer-supprt-tucson</t>
+  </si>
+  <si>
+    <t>Organizer (Conversational Spanish Required)</t>
+  </si>
+  <si>
+    <t>Housing Leadership Council of San Mateo County</t>
+  </si>
+  <si>
+    <t>San Mateo, CA</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22a1975bfc1b4fa79fcf798914d1685e-organizer-conversational-spanish-required-housing-leadership-council-of-san-mateo-county-san-mateo</t>
+  </si>
+  <si>
     <t>Outdoor Education Teacher/Naturalist</t>
   </si>
   <si>
@@ -1609,6 +2233,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0ebcbdb4524e42658cc46d306b716f23-part-time-facilitator-girls-inc-of-long-island-deer-park</t>
   </si>
   <si>
+    <t>Part-Time Program Facilitator</t>
+  </si>
+  <si>
+    <t>Live Out Loud (New York based)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e612c09652d4ae5a3e59f375e6a330b-part-time-program-facilitator-live-out-loud-new-york-based-new-york</t>
+  </si>
+  <si>
     <t>Part-time Youth Advisor</t>
   </si>
   <si>
@@ -1639,6 +2278,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/bf484e07a6354e598af9673e55798971-patient-meal-coordinator-culinary-care-chicago</t>
   </si>
   <si>
+    <t>Philanthropy &amp; Prospect Development Coordinator</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eff2fd825abb4fd9b7b9288daabb545f-philanthropy-prospect-development-coordinator-kesem-national-covina</t>
+  </si>
+  <si>
+    <t>Physical Education/Life Skills Teacher</t>
+  </si>
+  <si>
+    <t>St. James School Philadelphia</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a89ff44609014764b9c98b5474be9b71-physical-educationlife-skills-teacher-st-james-school-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>Politcal Canvasser</t>
   </si>
   <si>
@@ -1705,9 +2365,6 @@
     <t>Houston, Texas</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Education, Entrepreneurship</t>
   </si>
   <si>
@@ -1741,6 +2398,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/b4a6996f8eec4b4bb5a114ceb2106e67-programme-delivery-lead-thailand-futuresense-foundation-mae-sariang</t>
   </si>
   <si>
+    <t>Protection and Emerging Technologies Officer</t>
+  </si>
+  <si>
+    <t>ICRC - International Committee of the Red Cross</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a55f35934394f1c99156aa9561163f6-protection-and-emerging-technologies-officer-icrc-international-committee-of-the-red-cross-washington</t>
+  </si>
+  <si>
+    <t>Public Interest Advocate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 43500.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b1e5b5d9cbc4143a12c89255c3594e1-public-interest-advocate-us-pirg-raleigh</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1928ad9b68564091b7cb7b9b324cbbf3-public-interest-advocate-us-pirg-seattle</t>
+  </si>
+  <si>
+    <t>Public Policy Fellowship</t>
+  </si>
+  <si>
+    <t>National Disability Institute</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f61d4b76cccf42b18bb93ed2ac9c3632-public-policy-fellowship-national-disability-institute-washington</t>
+  </si>
+  <si>
+    <t>Re-Engagement Specialist</t>
+  </si>
+  <si>
+    <t>Boston Private Industry Council</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f161d1d5ca849088f1b20c2baccdef7-re-engagement-specialist-boston-private-industry-council-boston</t>
+  </si>
+  <si>
     <t>Regional Coordinator, START Center Initiative</t>
   </si>
   <si>
@@ -1756,6 +2479,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/269973e59d8c4bd4b1efdc2d5fe74b61-regional-coordinator-start-center-initiative-big-picture-learning-providence</t>
   </si>
   <si>
+    <t>Regional Growth Lead</t>
+  </si>
+  <si>
+    <t>Basta</t>
+  </si>
+  <si>
+    <t>Remote (North Carolina)</t>
+  </si>
+  <si>
+    <t>USD 7000.00 - 7000.00/month</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1576fea585654789b5d404310a11cde2-regional-growth-lead-basta-new-york</t>
+  </si>
+  <si>
+    <t>Research Administrative Assistant</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>USD 40350.00 - 42750.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bbc687684c641b3bf94513ff0238f64-research-administrative-assistant-the-public-interest-network-denver</t>
+  </si>
+  <si>
+    <t>Senior Development Officer</t>
+  </si>
+  <si>
+    <t>ACLU of Georgia</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b34c27babadf430bb52b00f9d2d63855-senior-development-officer-aclu-of-georgia-atlanta</t>
+  </si>
+  <si>
     <t>Senior Manager of Events</t>
   </si>
   <si>
@@ -1768,9 +2542,6 @@
     <t>Senior Manager, Marketing &amp; Engagement</t>
   </si>
   <si>
-    <t>USD 75000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Family, Poverty</t>
   </si>
   <si>
@@ -1804,15 +2575,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/20d8ef52e9754f729cc7a1f4119ed576-senior-writer-institutional-giving-tenacity-inc-boston</t>
   </si>
   <si>
+    <t>Social Worker</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 66300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe91f15105504b81a83e9a9e5092f2db-social-worker-jewish-association-serving-the-aging-brooklyn</t>
+  </si>
+  <si>
     <t>Social Worker - Community Guardian Program</t>
   </si>
   <si>
-    <t>Jewish Association Serving the Aging</t>
-  </si>
-  <si>
-    <t>USD 66300.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/561988af32044cffbfb87dbc976317c8-social-worker-community-guardian-program-jewish-association-serving-the-aging-new-york</t>
   </si>
   <si>
@@ -1846,6 +2626,63 @@
     <t>https://www.idealist.org/en/nonprofit-job/591f8e06b67d4ba8a7790f2a891d9a78-staff-attorney-alameda-county-homeless-action-center-berkeley</t>
   </si>
   <si>
+    <t>Storytelling &amp; Content Lead</t>
+  </si>
+  <si>
+    <t>Thanda After-School</t>
+  </si>
+  <si>
+    <t>Hibberdene, KwaZulu-Natal, ZA</t>
+  </si>
+  <si>
+    <t>ZAR 23000.00 - 30000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0634cda514014810a12d60a89755b1ef-storytelling-content-lead-thanda-after-school-hibberdene</t>
+  </si>
+  <si>
+    <t>SUPPORT SPECIALIST - METROPOLITAN HOUSING ACCESS PROGRAM (MHAP)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96053b3ea4574b31abfa488b0b953d35-support-specialist-metropolitan-housing-access-program-mhap-housing-counseling-services-inc-washington</t>
+  </si>
+  <si>
+    <t>Temporary Program Officer | 6-months | Hybrid | Public Health Non-profit</t>
+  </si>
+  <si>
+    <t>TSS - Temporary Staffing + Search</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1266fb2791c24d9bbe6708c0b834bec8-temporary-program-officer-6-months-hybrid-public-health-non-profit-tss-temporary-staffing-search-new-york</t>
+  </si>
+  <si>
+    <t>Training &amp; Clinical Coaching Coordinator - Clinical Supports Program</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11a002aea69c436bbfc45777c1578b01-training-clinical-coaching-coordinator-clinical-supports-program-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Trauma Counselor - SWF</t>
+  </si>
+  <si>
+    <t>Staten Island, New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/397573e16e39459bb4ad501a4d9addcf-trauma-counselor-swf-safe-horizon-staten-island</t>
+  </si>
+  <si>
     <t>U Street Main Street Manager</t>
   </si>
   <si>
@@ -1858,6 +2695,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/58e835e5af3140fd9af5017569327cf8-u-street-main-street-manager-district-bridges-washington</t>
   </si>
   <si>
+    <t>UX/UI Web Designer</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5588e91abdf84a26ae5817803a235996-uxui-web-designer-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Vice President -- National Civic Art Society -- Classical Public Art and Architecture</t>
   </si>
   <si>
@@ -1891,6 +2746,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/543fc05cc6dc4b729a6107be4c6cd9c4-vp-clinical-strategy-education-living-beyond-breast-cancer-bala-cynwyd</t>
   </si>
   <si>
+    <t>Waste is Out of Fashion Campaign Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3cb6f9067734e7bad34a2af5002ce3f-waste-is-out-of-fashion-campaign-associate-us-pirg-portland</t>
+  </si>
+  <si>
     <t>Wellbeing Navigator</t>
   </si>
   <si>
@@ -1907,6 +2768,54 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/f725b8ceebbc4dc9a33ac6090651dfca-wellbeing-navigator-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Youth Community Organizer</t>
+  </si>
+  <si>
+    <t>RISE Colorado</t>
+  </si>
+  <si>
+    <t>Aurora, Colorado</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b4fba50ee8c44d1acbafb4c052735ea-youth-community-organizer-rise-colorado-aurora</t>
+  </si>
+  <si>
+    <t>Youth Vote Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60b6bcc203ed41b886f13c4368d2bab2-youth-vote-organizer-student-pirgs-atlanta</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/359e9bb6b0314a3ab2becf2c820b6f05-youth-vote-organizer-student-pirgs-austin</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d13945c13b1426d9efe70b4d3f9f6eb-youth-vote-organizer-student-pirgs-tampa</t>
+  </si>
+  <si>
+    <t>Zero Waste Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5e50151a6464bb3941ce48af7a106ae-zero-waste-associate-us-pirg-los-angeles</t>
   </si>
 </sst>
 </file>
@@ -3494,7 +4403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3533,8 +4442,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3542,7 +4477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3583,370 +4518,370 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F6" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" t="s">
         <v>266</v>
       </c>
-      <c r="E7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F7" t="s">
-        <v>296</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F8" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B9" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="D9" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F9" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C10" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F10" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C11" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F11" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C13" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="D13" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C14" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D14" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F14" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B15" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F15" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>346</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C16" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D16" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F16" t="s">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B17" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D17" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F17" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3957,10 +4892,10 @@
         <v>358</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D18" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s">
         <v>360</v>
@@ -3969,1318 +4904,3020 @@
         <v>361</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B19" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C19" t="s">
         <v>365</v>
       </c>
       <c r="D19" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
+        <v>360</v>
+      </c>
+      <c r="F19" t="s">
+        <v>361</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="F19" t="s">
-        <v>367</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B20" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C20" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="F20" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B21" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C21" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D21" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="F21" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="B22" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="C22" t="s">
-        <v>272</v>
+        <v>371</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="F22" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="B23" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="C23" t="s">
-        <v>385</v>
+        <v>278</v>
       </c>
       <c r="D23" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E23" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="F23" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="B24" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D24" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E24" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="F24" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="C25" t="s">
-        <v>278</v>
+        <v>376</v>
       </c>
       <c r="D25" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E25" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="F25" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D26" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E26" t="s">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="F26" t="s">
-        <v>399</v>
+        <v>361</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B27" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="C27" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="D27" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="F27" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="B28" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="C28" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="D28" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="F28" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B29" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C29" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="D29" t="s">
-        <v>266</v>
+        <v>393</v>
       </c>
       <c r="E29" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="F29" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="B30" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="C30" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="D30" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s">
-        <v>290</v>
+        <v>400</v>
       </c>
       <c r="F30" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="B31" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="C31" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="D31" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E31" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="F31" t="s">
-        <v>423</v>
+        <v>361</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="B32" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="C32" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="D32" t="s">
+        <v>272</v>
+      </c>
+      <c r="E32" t="s">
+        <v>409</v>
+      </c>
+      <c r="F32" t="s">
         <v>266</v>
       </c>
-      <c r="E32" t="s">
-        <v>427</v>
-      </c>
-      <c r="F32" t="s">
-        <v>428</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="B33" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="C33" t="s">
-        <v>359</v>
+        <v>413</v>
       </c>
       <c r="D33" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E33" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="F33" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="B34" t="s">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="C34" t="s">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="F34" t="s">
-        <v>326</v>
+        <v>418</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="B35" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="C35" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="D35" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s">
-        <v>312</v>
+        <v>422</v>
       </c>
       <c r="F35" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="B36" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C36" t="s">
-        <v>272</v>
+        <v>427</v>
       </c>
       <c r="D36" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="F36" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>431</v>
       </c>
       <c r="B37" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="C37" t="s">
-        <v>447</v>
+        <v>374</v>
       </c>
       <c r="D37" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E37" t="s">
-        <v>290</v>
+        <v>433</v>
       </c>
       <c r="F37" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>431</v>
       </c>
       <c r="B38" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C38" t="s">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="D38" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E38" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F38" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B39" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="C39" t="s">
-        <v>300</v>
+        <v>443</v>
       </c>
       <c r="D39" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E39" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="B40" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C40" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="D40" t="s">
+        <v>272</v>
+      </c>
+      <c r="E40" t="s">
         <v>266</v>
       </c>
-      <c r="E40" t="s">
-        <v>461</v>
-      </c>
       <c r="F40" t="s">
-        <v>428</v>
+        <v>266</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="B41" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C41" t="s">
-        <v>359</v>
+        <v>443</v>
       </c>
       <c r="D41" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="E41" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F41" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B42" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="C42" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="D42" t="s">
-        <v>471</v>
+        <v>272</v>
       </c>
       <c r="E42" t="s">
-        <v>290</v>
+        <v>458</v>
       </c>
       <c r="F42" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B43" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>443</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E43" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="F43" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="B44" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="C44" t="s">
-        <v>481</v>
+        <v>278</v>
       </c>
       <c r="D44" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E44" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="F44" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B45" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="C45" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="D45" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E45" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="F45" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="B46" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="C46" t="s">
-        <v>493</v>
+        <v>374</v>
       </c>
       <c r="D46" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" t="s">
         <v>266</v>
       </c>
-      <c r="E46" t="s">
-        <v>306</v>
-      </c>
       <c r="F46" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>448</v>
       </c>
       <c r="C47" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="D47" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" t="s">
+        <v>480</v>
+      </c>
+      <c r="F47" t="s">
         <v>266</v>
       </c>
-      <c r="E47" t="s">
-        <v>496</v>
-      </c>
-      <c r="F47" t="s">
-        <v>326</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B48" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="C48" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D48" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" t="s">
+        <v>484</v>
+      </c>
+      <c r="F48" t="s">
         <v>266</v>
       </c>
-      <c r="E48" t="s">
-        <v>499</v>
-      </c>
-      <c r="F48" t="s">
-        <v>457</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="B49" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C49" t="s">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E49" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="F49" t="s">
-        <v>290</v>
+        <v>489</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B50" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="C50" t="s">
-        <v>507</v>
+        <v>443</v>
       </c>
       <c r="D50" t="s">
+        <v>393</v>
+      </c>
+      <c r="E50" t="s">
         <v>266</v>
       </c>
-      <c r="E50" t="s">
-        <v>508</v>
-      </c>
       <c r="F50" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="B51" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C51" t="s">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E51" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="F51" t="s">
-        <v>290</v>
+        <v>498</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="B52" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C52" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="D52" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="F52" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="B53" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="C53" t="s">
-        <v>278</v>
+        <v>507</v>
       </c>
       <c r="D53" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" t="s">
         <v>266</v>
       </c>
-      <c r="E53" t="s">
-        <v>523</v>
-      </c>
       <c r="F53" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="B54" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="C54" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="D54" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E54" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="F54" t="s">
-        <v>326</v>
+        <v>513</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C55" t="s">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="D55" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E55" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="F55" t="s">
-        <v>290</v>
+        <v>517</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C56" t="s">
-        <v>537</v>
+        <v>457</v>
       </c>
       <c r="D56" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F56" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="C57" t="s">
-        <v>543</v>
+        <v>443</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E57" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="F57" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C58" t="s">
-        <v>547</v>
+        <v>399</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="E58" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="F58" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="B59" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="C59" t="s">
-        <v>551</v>
+        <v>443</v>
       </c>
       <c r="D59" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E59" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="F59" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="B60" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C60" t="s">
-        <v>556</v>
+        <v>374</v>
       </c>
       <c r="D60" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E60" t="s">
-        <v>557</v>
+        <v>488</v>
       </c>
       <c r="F60" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="B61" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="C61" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="D61" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E61" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="F61" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="B62" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="C62" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="D62" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="F62" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="B63" t="s">
-        <v>486</v>
+        <v>346</v>
       </c>
       <c r="C63" t="s">
-        <v>572</v>
+        <v>347</v>
       </c>
       <c r="D63" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E63" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="F63" t="s">
-        <v>489</v>
+        <v>349</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="B64" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="C64" t="s">
-        <v>577</v>
+        <v>374</v>
       </c>
       <c r="D64" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E64" t="s">
-        <v>578</v>
+        <v>335</v>
       </c>
       <c r="F64" t="s">
-        <v>326</v>
+        <v>558</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B65" t="s">
-        <v>305</v>
+        <v>561</v>
       </c>
       <c r="C65" t="s">
         <v>278</v>
       </c>
       <c r="D65" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E65" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="F65" t="s">
-        <v>307</v>
+        <v>563</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="B66" t="s">
-        <v>421</v>
+        <v>566</v>
       </c>
       <c r="C66" t="s">
-        <v>342</v>
+        <v>443</v>
       </c>
       <c r="D66" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="F66" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="B67" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="C67" t="s">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="D67" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>366</v>
+        <v>572</v>
       </c>
       <c r="F67" t="s">
-        <v>290</v>
+        <v>573</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>590</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="C68" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="D68" t="s">
+        <v>272</v>
+      </c>
+      <c r="E68" t="s">
         <v>266</v>
       </c>
-      <c r="E68" t="s">
-        <v>593</v>
-      </c>
       <c r="F68" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>596</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="C69" t="s">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="D69" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="F69" t="s">
-        <v>290</v>
+        <v>581</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>600</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="C70" t="s">
-        <v>592</v>
+        <v>378</v>
       </c>
       <c r="D70" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="E70" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="F70" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B71" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C71" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="D71" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E71" t="s">
-        <v>607</v>
+        <v>342</v>
       </c>
       <c r="F71" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="B72" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="C72" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="D72" t="s">
-        <v>266</v>
+        <v>393</v>
       </c>
       <c r="E72" t="s">
-        <v>398</v>
+        <v>594</v>
       </c>
       <c r="F72" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="B73" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="C73" t="s">
-        <v>365</v>
+        <v>473</v>
       </c>
       <c r="D73" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E73" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="F73" t="s">
-        <v>617</v>
+        <v>313</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="B74" t="s">
-        <v>620</v>
+        <v>358</v>
       </c>
       <c r="C74" t="s">
-        <v>621</v>
+        <v>374</v>
       </c>
       <c r="D74" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>622</v>
+        <v>404</v>
       </c>
       <c r="F74" t="s">
-        <v>623</v>
+        <v>361</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>603</v>
+      </c>
+      <c r="B75" t="s">
+        <v>604</v>
+      </c>
+      <c r="C75" t="s">
+        <v>374</v>
+      </c>
+      <c r="D75" t="s">
+        <v>272</v>
+      </c>
+      <c r="E75" t="s">
+        <v>605</v>
+      </c>
+      <c r="F75" t="s">
+        <v>606</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>608</v>
+      </c>
+      <c r="B76" t="s">
+        <v>609</v>
+      </c>
+      <c r="C76" t="s">
+        <v>610</v>
+      </c>
+      <c r="D76" t="s">
+        <v>353</v>
+      </c>
+      <c r="E76" t="s">
+        <v>266</v>
+      </c>
+      <c r="F76" t="s">
+        <v>611</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>613</v>
+      </c>
+      <c r="B77" t="s">
+        <v>614</v>
+      </c>
+      <c r="C77" t="s">
+        <v>290</v>
+      </c>
+      <c r="D77" t="s">
+        <v>272</v>
+      </c>
+      <c r="E77" t="s">
+        <v>615</v>
+      </c>
+      <c r="F77" t="s">
+        <v>266</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>617</v>
+      </c>
+      <c r="B78" t="s">
+        <v>618</v>
+      </c>
+      <c r="C78" t="s">
+        <v>278</v>
+      </c>
+      <c r="D78" t="s">
+        <v>272</v>
+      </c>
+      <c r="E78" t="s">
+        <v>619</v>
+      </c>
+      <c r="F78" t="s">
+        <v>620</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>622</v>
+      </c>
+      <c r="B79" t="s">
+        <v>623</v>
+      </c>
+      <c r="C79" t="s">
+        <v>290</v>
+      </c>
+      <c r="D79" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" t="s">
+        <v>624</v>
+      </c>
+      <c r="F79" t="s">
         <v>625</v>
       </c>
-      <c r="B75" t="s">
+      <c r="H79" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="C75" t="s">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>627</v>
       </c>
-      <c r="D75" t="s">
+      <c r="B80" t="s">
+        <v>557</v>
+      </c>
+      <c r="C80" t="s">
+        <v>374</v>
+      </c>
+      <c r="D80" t="s">
+        <v>272</v>
+      </c>
+      <c r="E80" t="s">
+        <v>628</v>
+      </c>
+      <c r="F80" t="s">
+        <v>401</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>630</v>
+      </c>
+      <c r="B81" t="s">
+        <v>631</v>
+      </c>
+      <c r="C81" t="s">
+        <v>632</v>
+      </c>
+      <c r="D81" t="s">
+        <v>272</v>
+      </c>
+      <c r="E81" t="s">
+        <v>633</v>
+      </c>
+      <c r="F81" t="s">
+        <v>634</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>636</v>
+      </c>
+      <c r="B82" t="s">
+        <v>637</v>
+      </c>
+      <c r="C82" t="s">
+        <v>638</v>
+      </c>
+      <c r="D82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E82" t="s">
+        <v>639</v>
+      </c>
+      <c r="F82" t="s">
+        <v>640</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>642</v>
+      </c>
+      <c r="B83" t="s">
+        <v>643</v>
+      </c>
+      <c r="C83" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" t="s">
+        <v>272</v>
+      </c>
+      <c r="E83" t="s">
+        <v>644</v>
+      </c>
+      <c r="F83" t="s">
+        <v>645</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>647</v>
+      </c>
+      <c r="B84" t="s">
+        <v>648</v>
+      </c>
+      <c r="C84" t="s">
+        <v>649</v>
+      </c>
+      <c r="D84" t="s">
+        <v>272</v>
+      </c>
+      <c r="E84" t="s">
+        <v>329</v>
+      </c>
+      <c r="F84" t="s">
+        <v>349</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>651</v>
+      </c>
+      <c r="B85" t="s">
+        <v>652</v>
+      </c>
+      <c r="C85" t="s">
+        <v>374</v>
+      </c>
+      <c r="D85" t="s">
+        <v>272</v>
+      </c>
+      <c r="E85" t="s">
+        <v>653</v>
+      </c>
+      <c r="F85" t="s">
+        <v>654</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>656</v>
+      </c>
+      <c r="B86" t="s">
+        <v>657</v>
+      </c>
+      <c r="C86" t="s">
+        <v>374</v>
+      </c>
+      <c r="D86" t="s">
+        <v>272</v>
+      </c>
+      <c r="E86" t="s">
+        <v>658</v>
+      </c>
+      <c r="F86" t="s">
+        <v>659</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>661</v>
+      </c>
+      <c r="B87" t="s">
+        <v>346</v>
+      </c>
+      <c r="C87" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" t="s">
+        <v>272</v>
+      </c>
+      <c r="E87" t="s">
+        <v>662</v>
+      </c>
+      <c r="F87" t="s">
+        <v>349</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>664</v>
+      </c>
+      <c r="B88" t="s">
+        <v>665</v>
+      </c>
+      <c r="C88" t="s">
+        <v>290</v>
+      </c>
+      <c r="D88" t="s">
+        <v>272</v>
+      </c>
+      <c r="E88" t="s">
+        <v>666</v>
+      </c>
+      <c r="F88" t="s">
+        <v>667</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>669</v>
+      </c>
+      <c r="B89" t="s">
+        <v>670</v>
+      </c>
+      <c r="C89" t="s">
+        <v>378</v>
+      </c>
+      <c r="D89" t="s">
+        <v>272</v>
+      </c>
+      <c r="E89" t="s">
         <v>266</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F89" t="s">
+        <v>671</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>673</v>
+      </c>
+      <c r="B90" t="s">
+        <v>674</v>
+      </c>
+      <c r="C90" t="s">
+        <v>675</v>
+      </c>
+      <c r="D90" t="s">
+        <v>272</v>
+      </c>
+      <c r="E90" t="s">
+        <v>624</v>
+      </c>
+      <c r="F90" t="s">
+        <v>676</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>678</v>
+      </c>
+      <c r="B91" t="s">
+        <v>593</v>
+      </c>
+      <c r="C91" t="s">
+        <v>323</v>
+      </c>
+      <c r="D91" t="s">
+        <v>272</v>
+      </c>
+      <c r="E91" t="s">
+        <v>615</v>
+      </c>
+      <c r="F91" t="s">
+        <v>595</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>680</v>
+      </c>
+      <c r="B92" t="s">
+        <v>681</v>
+      </c>
+      <c r="C92" t="s">
+        <v>290</v>
+      </c>
+      <c r="D92" t="s">
+        <v>272</v>
+      </c>
+      <c r="E92" t="s">
+        <v>682</v>
+      </c>
+      <c r="F92" t="s">
+        <v>266</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>684</v>
+      </c>
+      <c r="B93" t="s">
+        <v>685</v>
+      </c>
+      <c r="C93" t="s">
+        <v>443</v>
+      </c>
+      <c r="D93" t="s">
+        <v>272</v>
+      </c>
+      <c r="E93" t="s">
+        <v>686</v>
+      </c>
+      <c r="F93" t="s">
+        <v>266</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>688</v>
+      </c>
+      <c r="B94" t="s">
+        <v>689</v>
+      </c>
+      <c r="C94" t="s">
+        <v>690</v>
+      </c>
+      <c r="D94" t="s">
+        <v>272</v>
+      </c>
+      <c r="E94" t="s">
+        <v>691</v>
+      </c>
+      <c r="F94" t="s">
+        <v>692</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>694</v>
+      </c>
+      <c r="B95" t="s">
+        <v>695</v>
+      </c>
+      <c r="C95" t="s">
+        <v>696</v>
+      </c>
+      <c r="D95" t="s">
+        <v>272</v>
+      </c>
+      <c r="E95" t="s">
+        <v>697</v>
+      </c>
+      <c r="F95" t="s">
+        <v>698</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>700</v>
+      </c>
+      <c r="B96" t="s">
+        <v>448</v>
+      </c>
+      <c r="C96" t="s">
+        <v>374</v>
+      </c>
+      <c r="D96" t="s">
+        <v>272</v>
+      </c>
+      <c r="E96" t="s">
+        <v>701</v>
+      </c>
+      <c r="F96" t="s">
+        <v>266</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>703</v>
+      </c>
+      <c r="B97" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" t="s">
+        <v>352</v>
+      </c>
+      <c r="D97" t="s">
+        <v>353</v>
+      </c>
+      <c r="E97" t="s">
+        <v>704</v>
+      </c>
+      <c r="F97" t="s">
+        <v>355</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>706</v>
+      </c>
+      <c r="B98" t="s">
+        <v>707</v>
+      </c>
+      <c r="C98" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" t="s">
+        <v>272</v>
+      </c>
+      <c r="E98" t="s">
+        <v>708</v>
+      </c>
+      <c r="F98" t="s">
+        <v>266</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>710</v>
+      </c>
+      <c r="B99" t="s">
+        <v>711</v>
+      </c>
+      <c r="C99" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" t="s">
+        <v>272</v>
+      </c>
+      <c r="E99" t="s">
+        <v>712</v>
+      </c>
+      <c r="F99" t="s">
+        <v>713</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>715</v>
+      </c>
+      <c r="B100" t="s">
+        <v>351</v>
+      </c>
+      <c r="C100" t="s">
+        <v>352</v>
+      </c>
+      <c r="D100" t="s">
+        <v>353</v>
+      </c>
+      <c r="E100" t="s">
+        <v>716</v>
+      </c>
+      <c r="F100" t="s">
+        <v>355</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>718</v>
+      </c>
+      <c r="B101" t="s">
+        <v>719</v>
+      </c>
+      <c r="C101" t="s">
+        <v>720</v>
+      </c>
+      <c r="D101" t="s">
+        <v>272</v>
+      </c>
+      <c r="E101" t="s">
+        <v>721</v>
+      </c>
+      <c r="F101" t="s">
+        <v>551</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>723</v>
+      </c>
+      <c r="B102" t="s">
+        <v>724</v>
+      </c>
+      <c r="C102" t="s">
+        <v>725</v>
+      </c>
+      <c r="D102" t="s">
+        <v>341</v>
+      </c>
+      <c r="E102" t="s">
+        <v>726</v>
+      </c>
+      <c r="F102" t="s">
+        <v>727</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>729</v>
+      </c>
+      <c r="B103" t="s">
+        <v>730</v>
+      </c>
+      <c r="C103" t="s">
+        <v>290</v>
+      </c>
+      <c r="D103" t="s">
+        <v>272</v>
+      </c>
+      <c r="E103" t="s">
+        <v>731</v>
+      </c>
+      <c r="F103" t="s">
+        <v>732</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>734</v>
+      </c>
+      <c r="B104" t="s">
+        <v>735</v>
+      </c>
+      <c r="C104" t="s">
+        <v>736</v>
+      </c>
+      <c r="D104" t="s">
+        <v>393</v>
+      </c>
+      <c r="E104" t="s">
+        <v>737</v>
+      </c>
+      <c r="F104" t="s">
+        <v>349</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>739</v>
+      </c>
+      <c r="B105" t="s">
+        <v>740</v>
+      </c>
+      <c r="C105" t="s">
+        <v>290</v>
+      </c>
+      <c r="D105" t="s">
+        <v>393</v>
+      </c>
+      <c r="E105" t="s">
+        <v>741</v>
+      </c>
+      <c r="F105" t="s">
+        <v>742</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>744</v>
+      </c>
+      <c r="B106" t="s">
+        <v>745</v>
+      </c>
+      <c r="C106" t="s">
+        <v>290</v>
+      </c>
+      <c r="D106" t="s">
+        <v>393</v>
+      </c>
+      <c r="E106" t="s">
+        <v>746</v>
+      </c>
+      <c r="F106" t="s">
+        <v>266</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>748</v>
+      </c>
+      <c r="B107" t="s">
+        <v>749</v>
+      </c>
+      <c r="C107" t="s">
+        <v>750</v>
+      </c>
+      <c r="D107" t="s">
+        <v>393</v>
+      </c>
+      <c r="E107" t="s">
+        <v>751</v>
+      </c>
+      <c r="F107" t="s">
+        <v>752</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>754</v>
+      </c>
+      <c r="B108" t="s">
+        <v>525</v>
+      </c>
+      <c r="C108" t="s">
+        <v>443</v>
+      </c>
+      <c r="D108" t="s">
+        <v>272</v>
+      </c>
+      <c r="E108" t="s">
+        <v>755</v>
+      </c>
+      <c r="F108" t="s">
+        <v>527</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>757</v>
+      </c>
+      <c r="B109" t="s">
+        <v>758</v>
+      </c>
+      <c r="C109" t="s">
+        <v>363</v>
+      </c>
+      <c r="D109" t="s">
+        <v>272</v>
+      </c>
+      <c r="E109" t="s">
+        <v>273</v>
+      </c>
+      <c r="F109" t="s">
+        <v>759</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>761</v>
+      </c>
+      <c r="B110" t="s">
+        <v>762</v>
+      </c>
+      <c r="C110" t="s">
+        <v>763</v>
+      </c>
+      <c r="D110" t="s">
+        <v>341</v>
+      </c>
+      <c r="E110" t="s">
+        <v>764</v>
+      </c>
+      <c r="F110" t="s">
+        <v>765</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>761</v>
+      </c>
+      <c r="B111" t="s">
+        <v>762</v>
+      </c>
+      <c r="C111" t="s">
+        <v>767</v>
+      </c>
+      <c r="D111" t="s">
+        <v>341</v>
+      </c>
+      <c r="E111" t="s">
+        <v>764</v>
+      </c>
+      <c r="F111" t="s">
+        <v>765</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>769</v>
+      </c>
+      <c r="B112" t="s">
+        <v>770</v>
+      </c>
+      <c r="C112" t="s">
+        <v>771</v>
+      </c>
+      <c r="D112" t="s">
+        <v>272</v>
+      </c>
+      <c r="E112" t="s">
+        <v>772</v>
+      </c>
+      <c r="F112" t="s">
+        <v>266</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>774</v>
+      </c>
+      <c r="B113" t="s">
+        <v>775</v>
+      </c>
+      <c r="C113" t="s">
+        <v>776</v>
+      </c>
+      <c r="D113" t="s">
+        <v>272</v>
+      </c>
+      <c r="E113" t="s">
+        <v>777</v>
+      </c>
+      <c r="F113" t="s">
+        <v>778</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>780</v>
+      </c>
+      <c r="B114" t="s">
+        <v>781</v>
+      </c>
+      <c r="C114" t="s">
+        <v>782</v>
+      </c>
+      <c r="D114" t="s">
+        <v>272</v>
+      </c>
+      <c r="E114" t="s">
+        <v>721</v>
+      </c>
+      <c r="F114" t="s">
+        <v>783</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>785</v>
+      </c>
+      <c r="B115" t="s">
+        <v>786</v>
+      </c>
+      <c r="C115" t="s">
+        <v>374</v>
+      </c>
+      <c r="D115" t="s">
+        <v>272</v>
+      </c>
+      <c r="E115" t="s">
+        <v>787</v>
+      </c>
+      <c r="F115" t="s">
+        <v>788</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>790</v>
+      </c>
+      <c r="B116" t="s">
+        <v>637</v>
+      </c>
+      <c r="C116" t="s">
+        <v>791</v>
+      </c>
+      <c r="D116" t="s">
+        <v>272</v>
+      </c>
+      <c r="E116" t="s">
+        <v>792</v>
+      </c>
+      <c r="F116" t="s">
+        <v>640</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>794</v>
+      </c>
+      <c r="B117" t="s">
+        <v>795</v>
+      </c>
+      <c r="C117" t="s">
+        <v>317</v>
+      </c>
+      <c r="D117" t="s">
+        <v>272</v>
+      </c>
+      <c r="E117" t="s">
+        <v>796</v>
+      </c>
+      <c r="F117" t="s">
+        <v>266</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>798</v>
+      </c>
+      <c r="B118" t="s">
+        <v>799</v>
+      </c>
+      <c r="C118" t="s">
+        <v>800</v>
+      </c>
+      <c r="D118" t="s">
+        <v>272</v>
+      </c>
+      <c r="E118" t="s">
+        <v>801</v>
+      </c>
+      <c r="F118" t="s">
+        <v>802</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>798</v>
+      </c>
+      <c r="B119" t="s">
+        <v>799</v>
+      </c>
+      <c r="C119" t="s">
+        <v>378</v>
+      </c>
+      <c r="D119" t="s">
+        <v>272</v>
+      </c>
+      <c r="E119" t="s">
+        <v>801</v>
+      </c>
+      <c r="F119" t="s">
+        <v>802</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>805</v>
+      </c>
+      <c r="B120" t="s">
+        <v>806</v>
+      </c>
+      <c r="C120" t="s">
+        <v>443</v>
+      </c>
+      <c r="D120" t="s">
+        <v>807</v>
+      </c>
+      <c r="E120" t="s">
+        <v>808</v>
+      </c>
+      <c r="F120" t="s">
+        <v>809</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>811</v>
+      </c>
+      <c r="B121" t="s">
+        <v>812</v>
+      </c>
+      <c r="C121" t="s">
+        <v>278</v>
+      </c>
+      <c r="D121" t="s">
+        <v>272</v>
+      </c>
+      <c r="E121" t="s">
+        <v>813</v>
+      </c>
+      <c r="F121" t="s">
+        <v>814</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>816</v>
+      </c>
+      <c r="B122" t="s">
+        <v>817</v>
+      </c>
+      <c r="C122" t="s">
+        <v>818</v>
+      </c>
+      <c r="D122" t="s">
+        <v>272</v>
+      </c>
+      <c r="E122" t="s">
+        <v>819</v>
+      </c>
+      <c r="F122" t="s">
+        <v>349</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>821</v>
+      </c>
+      <c r="B123" t="s">
+        <v>822</v>
+      </c>
+      <c r="C123" t="s">
+        <v>823</v>
+      </c>
+      <c r="D123" t="s">
+        <v>353</v>
+      </c>
+      <c r="E123" t="s">
+        <v>824</v>
+      </c>
+      <c r="F123" t="s">
+        <v>825</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>827</v>
+      </c>
+      <c r="B124" t="s">
+        <v>828</v>
+      </c>
+      <c r="C124" t="s">
+        <v>365</v>
+      </c>
+      <c r="D124" t="s">
+        <v>272</v>
+      </c>
+      <c r="E124" t="s">
+        <v>829</v>
+      </c>
+      <c r="F124" t="s">
+        <v>830</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>832</v>
+      </c>
+      <c r="B125" t="s">
+        <v>833</v>
+      </c>
+      <c r="C125" t="s">
+        <v>834</v>
+      </c>
+      <c r="D125" t="s">
+        <v>272</v>
+      </c>
+      <c r="E125" t="s">
+        <v>835</v>
+      </c>
+      <c r="F125" t="s">
+        <v>836</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>838</v>
+      </c>
+      <c r="B126" t="s">
+        <v>328</v>
+      </c>
+      <c r="C126" t="s">
+        <v>290</v>
+      </c>
+      <c r="D126" t="s">
+        <v>272</v>
+      </c>
+      <c r="E126" t="s">
+        <v>839</v>
+      </c>
+      <c r="F126" t="s">
+        <v>330</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>841</v>
+      </c>
+      <c r="B127" t="s">
+        <v>530</v>
+      </c>
+      <c r="C127" t="s">
+        <v>399</v>
+      </c>
+      <c r="D127" t="s">
+        <v>272</v>
+      </c>
+      <c r="E127" t="s">
         <v>628</v>
       </c>
-      <c r="F75" t="s">
-        <v>629</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>630</v>
+      <c r="F127" t="s">
+        <v>842</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>844</v>
+      </c>
+      <c r="B128" t="s">
+        <v>845</v>
+      </c>
+      <c r="C128" t="s">
+        <v>457</v>
+      </c>
+      <c r="D128" t="s">
+        <v>272</v>
+      </c>
+      <c r="E128" t="s">
+        <v>444</v>
+      </c>
+      <c r="F128" t="s">
+        <v>266</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>847</v>
+      </c>
+      <c r="B129" t="s">
+        <v>848</v>
+      </c>
+      <c r="C129" t="s">
+        <v>849</v>
+      </c>
+      <c r="D129" t="s">
+        <v>272</v>
+      </c>
+      <c r="E129" t="s">
+        <v>850</v>
+      </c>
+      <c r="F129" t="s">
+        <v>851</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>853</v>
+      </c>
+      <c r="B130" t="s">
+        <v>854</v>
+      </c>
+      <c r="C130" t="s">
+        <v>855</v>
+      </c>
+      <c r="D130" t="s">
+        <v>272</v>
+      </c>
+      <c r="E130" t="s">
+        <v>856</v>
+      </c>
+      <c r="F130" t="s">
+        <v>266</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>858</v>
+      </c>
+      <c r="B131" t="s">
+        <v>854</v>
+      </c>
+      <c r="C131" t="s">
+        <v>290</v>
+      </c>
+      <c r="D131" t="s">
+        <v>272</v>
+      </c>
+      <c r="E131" t="s">
+        <v>856</v>
+      </c>
+      <c r="F131" t="s">
+        <v>266</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>860</v>
+      </c>
+      <c r="B132" t="s">
+        <v>861</v>
+      </c>
+      <c r="C132" t="s">
+        <v>849</v>
+      </c>
+      <c r="D132" t="s">
+        <v>393</v>
+      </c>
+      <c r="E132" t="s">
+        <v>737</v>
+      </c>
+      <c r="F132" t="s">
+        <v>862</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>864</v>
+      </c>
+      <c r="B133" t="s">
+        <v>865</v>
+      </c>
+      <c r="C133" t="s">
+        <v>866</v>
+      </c>
+      <c r="D133" t="s">
+        <v>272</v>
+      </c>
+      <c r="E133" t="s">
+        <v>867</v>
+      </c>
+      <c r="F133" t="s">
+        <v>868</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>870</v>
+      </c>
+      <c r="B134" t="s">
+        <v>871</v>
+      </c>
+      <c r="C134" t="s">
+        <v>872</v>
+      </c>
+      <c r="D134" t="s">
+        <v>272</v>
+      </c>
+      <c r="E134" t="s">
+        <v>873</v>
+      </c>
+      <c r="F134" t="s">
+        <v>475</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>875</v>
+      </c>
+      <c r="B135" t="s">
+        <v>557</v>
+      </c>
+      <c r="C135" t="s">
+        <v>374</v>
+      </c>
+      <c r="D135" t="s">
+        <v>272</v>
+      </c>
+      <c r="E135" t="s">
+        <v>463</v>
+      </c>
+      <c r="F135" t="s">
+        <v>558</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>877</v>
+      </c>
+      <c r="B136" t="s">
+        <v>878</v>
+      </c>
+      <c r="C136" t="s">
+        <v>290</v>
+      </c>
+      <c r="D136" t="s">
+        <v>341</v>
+      </c>
+      <c r="E136" t="s">
+        <v>879</v>
+      </c>
+      <c r="F136" t="s">
+        <v>880</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>882</v>
+      </c>
+      <c r="B137" t="s">
+        <v>412</v>
+      </c>
+      <c r="C137" t="s">
+        <v>290</v>
+      </c>
+      <c r="D137" t="s">
+        <v>272</v>
+      </c>
+      <c r="E137" t="s">
+        <v>883</v>
+      </c>
+      <c r="F137" t="s">
+        <v>266</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>885</v>
+      </c>
+      <c r="B138" t="s">
+        <v>412</v>
+      </c>
+      <c r="C138" t="s">
+        <v>886</v>
+      </c>
+      <c r="D138" t="s">
+        <v>272</v>
+      </c>
+      <c r="E138" t="s">
+        <v>887</v>
+      </c>
+      <c r="F138" t="s">
+        <v>415</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>889</v>
+      </c>
+      <c r="B139" t="s">
+        <v>890</v>
+      </c>
+      <c r="C139" t="s">
+        <v>374</v>
+      </c>
+      <c r="D139" t="s">
+        <v>272</v>
+      </c>
+      <c r="E139" t="s">
+        <v>488</v>
+      </c>
+      <c r="F139" t="s">
+        <v>891</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>893</v>
+      </c>
+      <c r="B140" t="s">
+        <v>894</v>
+      </c>
+      <c r="C140" t="s">
+        <v>895</v>
+      </c>
+      <c r="D140" t="s">
+        <v>807</v>
+      </c>
+      <c r="E140" t="s">
+        <v>896</v>
+      </c>
+      <c r="F140" t="s">
+        <v>897</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>899</v>
+      </c>
+      <c r="B141" t="s">
+        <v>900</v>
+      </c>
+      <c r="C141" t="s">
+        <v>443</v>
+      </c>
+      <c r="D141" t="s">
+        <v>272</v>
+      </c>
+      <c r="E141" t="s">
+        <v>901</v>
+      </c>
+      <c r="F141" t="s">
+        <v>902</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>904</v>
+      </c>
+      <c r="B142" t="s">
+        <v>905</v>
+      </c>
+      <c r="C142" t="s">
+        <v>906</v>
+      </c>
+      <c r="D142" t="s">
+        <v>272</v>
+      </c>
+      <c r="E142" t="s">
+        <v>907</v>
+      </c>
+      <c r="F142" t="s">
+        <v>908</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>910</v>
+      </c>
+      <c r="B143" t="s">
+        <v>799</v>
+      </c>
+      <c r="C143" t="s">
+        <v>371</v>
+      </c>
+      <c r="D143" t="s">
+        <v>272</v>
+      </c>
+      <c r="E143" t="s">
+        <v>404</v>
+      </c>
+      <c r="F143" t="s">
+        <v>361</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>912</v>
+      </c>
+      <c r="B144" t="s">
+        <v>913</v>
+      </c>
+      <c r="C144" t="s">
+        <v>914</v>
+      </c>
+      <c r="D144" t="s">
+        <v>272</v>
+      </c>
+      <c r="E144" t="s">
+        <v>915</v>
+      </c>
+      <c r="F144" t="s">
+        <v>916</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>918</v>
+      </c>
+      <c r="B145" t="s">
+        <v>919</v>
+      </c>
+      <c r="C145" t="s">
+        <v>920</v>
+      </c>
+      <c r="D145" t="s">
+        <v>272</v>
+      </c>
+      <c r="E145" t="s">
+        <v>921</v>
+      </c>
+      <c r="F145" t="s">
+        <v>922</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>924</v>
+      </c>
+      <c r="B146" t="s">
+        <v>925</v>
+      </c>
+      <c r="C146" t="s">
+        <v>834</v>
+      </c>
+      <c r="D146" t="s">
+        <v>272</v>
+      </c>
+      <c r="E146" t="s">
+        <v>404</v>
+      </c>
+      <c r="F146" t="s">
+        <v>926</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>924</v>
+      </c>
+      <c r="B147" t="s">
+        <v>925</v>
+      </c>
+      <c r="C147" t="s">
+        <v>928</v>
+      </c>
+      <c r="D147" t="s">
+        <v>272</v>
+      </c>
+      <c r="E147" t="s">
+        <v>404</v>
+      </c>
+      <c r="F147" t="s">
+        <v>926</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>924</v>
+      </c>
+      <c r="B148" t="s">
+        <v>925</v>
+      </c>
+      <c r="C148" t="s">
+        <v>930</v>
+      </c>
+      <c r="D148" t="s">
+        <v>272</v>
+      </c>
+      <c r="E148" t="s">
+        <v>404</v>
+      </c>
+      <c r="F148" t="s">
+        <v>926</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>932</v>
+      </c>
+      <c r="B149" t="s">
+        <v>799</v>
+      </c>
+      <c r="C149" t="s">
+        <v>457</v>
+      </c>
+      <c r="D149" t="s">
+        <v>272</v>
+      </c>
+      <c r="E149" t="s">
+        <v>404</v>
+      </c>
+      <c r="F149" t="s">
+        <v>361</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>933</v>
       </c>
     </row>
   </sheetData>
@@ -5360,6 +7997,80 @@
     <hyperlink ref="H73" r:id="rId72"/>
     <hyperlink ref="H74" r:id="rId73"/>
     <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
